--- a/JES.xlsx
+++ b/JES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jyoti Enclave Society\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DDF134B-9704-4650-806D-53D53E73E5ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5354F766-0FEE-4016-88B8-B85497867C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -167,8 +167,8 @@
   <authors>
     <author>Midnights</author>
     <author>LENOVO</author>
+    <author>lenovo</author>
     <author>admin 2</author>
-    <author>lenovo</author>
   </authors>
   <commentList>
     <comment ref="I2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
@@ -209,31 +209,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AP9" authorId="2" shapeId="0" xr:uid="{2EF39BCB-B03D-4948-97DC-D2DCD2C1BCD7}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>admin 2:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Cash with Rajeshji</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I13" authorId="3" shapeId="0" xr:uid="{9FB16F04-838F-4015-8DAE-AC1B99FAA369}">
+    <comment ref="I13" authorId="2" shapeId="0" xr:uid="{9FB16F04-838F-4015-8DAE-AC1B99FAA369}">
       <text>
         <r>
           <rPr>
@@ -576,7 +552,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AO30" authorId="2" shapeId="0" xr:uid="{51FBE73F-16FE-49AE-8311-02C1DB67519C}">
+    <comment ref="AO30" authorId="3" shapeId="0" xr:uid="{51FBE73F-16FE-49AE-8311-02C1DB67519C}">
       <text>
         <r>
           <rPr>
@@ -696,7 +672,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AN45" authorId="2" shapeId="0" xr:uid="{E161952F-2267-448D-89A2-31A67A602656}">
+    <comment ref="AN45" authorId="3" shapeId="0" xr:uid="{E161952F-2267-448D-89A2-31A67A602656}">
       <text>
         <r>
           <rPr>
@@ -893,7 +869,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T55" authorId="3" shapeId="0" xr:uid="{C9F4651D-2F07-4F8B-AD3A-30E9DE1E7770}">
+    <comment ref="T55" authorId="2" shapeId="0" xr:uid="{C9F4651D-2F07-4F8B-AD3A-30E9DE1E7770}">
       <text>
         <r>
           <rPr>
@@ -991,7 +967,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AO59" authorId="2" shapeId="0" xr:uid="{DA9A4A39-4361-457B-B1B6-141CC514D0A3}">
+    <comment ref="AO59" authorId="3" shapeId="0" xr:uid="{DA9A4A39-4361-457B-B1B6-141CC514D0A3}">
       <text>
         <r>
           <rPr>
@@ -1161,7 +1137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="409">
   <si>
     <t>Monthly Payment</t>
   </si>
@@ -1848,9 +1824,6 @@
   </si>
   <si>
     <t>SURESH JI KHANDELWAL</t>
-  </si>
-  <si>
-    <t>SURESHJIKHANDELWAL</t>
   </si>
   <si>
     <t>Plumber charges Pipe repairing 148 side</t>
@@ -2367,58 +2340,64 @@
     <t xml:space="preserve">Flat </t>
   </si>
   <si>
+    <t>ASHOK KUMAWAT</t>
+  </si>
+  <si>
+    <t>Electricity Bill Jun26</t>
+  </si>
+  <si>
+    <t>Electricity Bill Jul26</t>
+  </si>
+  <si>
+    <t>Vansh Pratap</t>
+  </si>
+  <si>
+    <t>147D</t>
+  </si>
+  <si>
+    <t>Arjun Swami</t>
+  </si>
+  <si>
+    <t>148D</t>
+  </si>
+  <si>
+    <t>Valuve Repairing Block106, Valuve500, Tape20,Ring10,Labour Chrge 260,Kamalji300</t>
+  </si>
+  <si>
+    <t>Electricity Bill Aug26</t>
+  </si>
+  <si>
+    <t>Valuve Bill</t>
+  </si>
+  <si>
+    <t>Zolto Valuve 900, Socket, T, Nipple 1,12,4 inch, Elbow, Tafflon, Labour300 (Zolto Valuve Warrenty 2 Years)</t>
+  </si>
+  <si>
+    <t>BODHURAM SAINI</t>
+  </si>
+  <si>
+    <t>SURESH KHANDELWAL</t>
+  </si>
+  <si>
+    <t>Society Tree cutting and trimming Phoolji (778863361)</t>
+  </si>
+  <si>
+    <t>Electricity Bill Sep26</t>
+  </si>
+  <si>
+    <t>Sep Pending</t>
+  </si>
+  <si>
+    <t>Jitendra Bhatt</t>
+  </si>
+  <si>
+    <t>105A</t>
+  </si>
+  <si>
     <t>Ravi Singh</t>
   </si>
   <si>
     <t>107C</t>
-  </si>
-  <si>
-    <t>ASHOK KUMAWAT</t>
-  </si>
-  <si>
-    <t>Electricity Bill Jun26</t>
-  </si>
-  <si>
-    <t>148E</t>
-  </si>
-  <si>
-    <t>Jun Month Late Payment Charge</t>
-  </si>
-  <si>
-    <t>Electricity Bill Jul26</t>
-  </si>
-  <si>
-    <t>Abhishek Pareek</t>
-  </si>
-  <si>
-    <t>Ashok Kumawat</t>
-  </si>
-  <si>
-    <t>105F</t>
-  </si>
-  <si>
-    <t>Vansh Pratap</t>
-  </si>
-  <si>
-    <t>147D</t>
-  </si>
-  <si>
-    <t>Arjun Swami</t>
-  </si>
-  <si>
-    <t>148D</t>
-  </si>
-  <si>
-    <t>May26 Payment Due</t>
-  </si>
-  <si>
-    <t>Jun,Jul Pending</t>
-  </si>
-  <si>
-    <t>Valuve Repairing Block106, Valuve500, Tape20,Ring10,Labour Chrge 260,Kamalji300</t>
-  </si>
-  <si>
-    <t>Jun Pending</t>
   </si>
 </sst>
 </file>
@@ -2434,18 +2413,11 @@
     <numFmt numFmtId="167" formatCode="[$₹-4009]\ #,##0.00"/>
     <numFmt numFmtId="168" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="38" x14ac:knownFonts="1">
+  <fonts count="37" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2879,7 +2851,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="102">
+  <borders count="103">
     <border>
       <left/>
       <right/>
@@ -4184,709 +4156,703 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="367">
+  <cellXfs count="369">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="14" fillId="15" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="15" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="13" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="13" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="13" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="13" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="13" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="13" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="15" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="15" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="8" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="7" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="21" fillId="16" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="22" fillId="16" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="15" fontId="6" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="5" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="15" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="15" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="15" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="5" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="17" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="17" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="15" fontId="6" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="5" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="17" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="14" fillId="16" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="14" fillId="19" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="16" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="19" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="15" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="25" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="24" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="25" fillId="19" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="24" fillId="19" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="8" fillId="13" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="7" fillId="13" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="15" fontId="25" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="24" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="25" fillId="19" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="24" fillId="19" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="15" fontId="25" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="24" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="25" fillId="16" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="24" fillId="16" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="25" fillId="19" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="24" fillId="19" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="11" fillId="0" borderId="60" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="17" fontId="10" fillId="0" borderId="60" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="42" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="16" fillId="0" borderId="60" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="17" fontId="15" fillId="0" borderId="60" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="11" fillId="0" borderId="61" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="17" fontId="10" fillId="0" borderId="61" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="26" fillId="20" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="25" fillId="20" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="17" fontId="22" fillId="16" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="21" fillId="16" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="22" fillId="16" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="21" fillId="16" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="22" fillId="16" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="21" fillId="16" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="66" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="17" fontId="22" fillId="16" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="66" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="17" fontId="21" fillId="16" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="72" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="72" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="65" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="65" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="13" fillId="16" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="12" fillId="16" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="16" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="12" fillId="16" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="6" fontId="35" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="34" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="17" fontId="36" fillId="15" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="35" fillId="15" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="27" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="27" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="27" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="27" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="27" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="27" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="27" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="27" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="27" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="27" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="27" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="16" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="27" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="15" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="15" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="27" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="15" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="15" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="16" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="15" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="81" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="34" fillId="15" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="81" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="15" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="15" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="18" borderId="87" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="16" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="16" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="16" borderId="88" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="89" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="88" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="27" borderId="89" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="16" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="16" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="83" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="83" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="28" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="83" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="34" fillId="28" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="83" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="15" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="15" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="15" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="15" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="15" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="15" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="81" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="81" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="81" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="35" fillId="18" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="17" fontId="35" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="81" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="34" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="8" fontId="35" fillId="0" borderId="90" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="34" fillId="0" borderId="90" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="36" fillId="16" borderId="82" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="35" fillId="16" borderId="82" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="34" fillId="0" borderId="81" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="27" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="82" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="82" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="91" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="17" fontId="35" fillId="0" borderId="92" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="35" fillId="0" borderId="81" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="94" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="21" fillId="16" borderId="95" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="34" fillId="0" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="85" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="17" fontId="21" fillId="16" borderId="96" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="34" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="21" fillId="16" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="34" fillId="0" borderId="90" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="98" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="15" fontId="35" fillId="0" borderId="81" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="35" fillId="0" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="30" borderId="92" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="30" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="30" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="81" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="82" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="35" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="82" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="91" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="17" fontId="36" fillId="0" borderId="92" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="36" fillId="0" borderId="81" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="94" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="22" fillId="16" borderId="95" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="35" fillId="0" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="85" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="17" fontId="22" fillId="16" borderId="96" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="35" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="22" fillId="16" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="35" fillId="0" borderId="90" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="98" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="36" fillId="0" borderId="81" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="36" fillId="0" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="30" borderId="92" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="30" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="30" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="81" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="34" fillId="15" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="19" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="15" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="18" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="19" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="15" borderId="87" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="27" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -4905,129 +4871,146 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="16" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="99" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="101" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="99" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="101" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -6317,139 +6300,139 @@
   <sheetData>
     <row r="3" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="318"/>
-      <c r="C4" s="319"/>
-      <c r="D4" s="319"/>
-      <c r="E4" s="319"/>
-      <c r="F4" s="320"/>
+      <c r="B4" s="315"/>
+      <c r="C4" s="316"/>
+      <c r="D4" s="316"/>
+      <c r="E4" s="316"/>
+      <c r="F4" s="317"/>
       <c r="G4" s="210"/>
     </row>
     <row r="5" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="321"/>
-      <c r="C5" s="322"/>
-      <c r="D5" s="322"/>
-      <c r="E5" s="322"/>
-      <c r="F5" s="323"/>
+      <c r="B5" s="318"/>
+      <c r="C5" s="319"/>
+      <c r="D5" s="319"/>
+      <c r="E5" s="319"/>
+      <c r="F5" s="320"/>
       <c r="G5" s="210"/>
     </row>
     <row r="6" spans="2:7" ht="26" x14ac:dyDescent="0.6">
-      <c r="B6" s="314">
+      <c r="B6" s="337">
         <v>1</v>
       </c>
-      <c r="C6" s="315"/>
-      <c r="D6" s="326" t="s">
+      <c r="C6" s="338"/>
+      <c r="D6" s="325" t="s">
         <v>0</v>
       </c>
-      <c r="E6" s="326"/>
-      <c r="F6" s="327"/>
+      <c r="E6" s="325"/>
+      <c r="F6" s="326"/>
     </row>
     <row r="7" spans="2:7" ht="26" x14ac:dyDescent="0.6">
-      <c r="B7" s="316">
+      <c r="B7" s="323">
         <v>2</v>
       </c>
-      <c r="C7" s="317">
+      <c r="C7" s="324">
         <v>2</v>
       </c>
-      <c r="D7" s="324" t="s">
+      <c r="D7" s="321" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="324"/>
-      <c r="F7" s="325"/>
+      <c r="E7" s="321"/>
+      <c r="F7" s="322"/>
     </row>
     <row r="8" spans="2:7" ht="26" x14ac:dyDescent="0.6">
-      <c r="B8" s="316">
+      <c r="B8" s="323">
         <v>3</v>
       </c>
-      <c r="C8" s="317">
+      <c r="C8" s="324">
         <v>3</v>
       </c>
-      <c r="D8" s="324" t="s">
+      <c r="D8" s="321" t="s">
         <v>2</v>
       </c>
-      <c r="E8" s="324"/>
-      <c r="F8" s="325"/>
+      <c r="E8" s="321"/>
+      <c r="F8" s="322"/>
     </row>
     <row r="9" spans="2:7" ht="26" x14ac:dyDescent="0.6">
-      <c r="B9" s="316">
+      <c r="B9" s="323">
         <v>4</v>
       </c>
-      <c r="C9" s="317">
+      <c r="C9" s="324">
         <v>4</v>
       </c>
-      <c r="D9" s="324" t="s">
+      <c r="D9" s="321" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="324"/>
-      <c r="F9" s="325"/>
+      <c r="E9" s="321"/>
+      <c r="F9" s="322"/>
     </row>
     <row r="10" spans="2:7" ht="26" x14ac:dyDescent="0.6">
-      <c r="B10" s="316">
+      <c r="B10" s="323">
         <v>5</v>
       </c>
-      <c r="C10" s="317">
+      <c r="C10" s="324">
         <v>5</v>
       </c>
-      <c r="D10" s="324" t="s">
+      <c r="D10" s="321" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="324"/>
-      <c r="F10" s="325"/>
+      <c r="E10" s="321"/>
+      <c r="F10" s="322"/>
     </row>
     <row r="11" spans="2:7" ht="26" x14ac:dyDescent="0.6">
-      <c r="B11" s="316">
+      <c r="B11" s="323">
         <v>6</v>
       </c>
-      <c r="C11" s="317">
+      <c r="C11" s="324">
         <v>6</v>
       </c>
-      <c r="D11" s="324" t="s">
+      <c r="D11" s="321" t="s">
         <v>5</v>
       </c>
-      <c r="E11" s="324"/>
-      <c r="F11" s="325"/>
+      <c r="E11" s="321"/>
+      <c r="F11" s="322"/>
     </row>
     <row r="12" spans="2:7" ht="26" x14ac:dyDescent="0.6">
-      <c r="B12" s="316">
+      <c r="B12" s="323">
         <v>7</v>
       </c>
-      <c r="C12" s="317">
+      <c r="C12" s="324">
         <v>7</v>
       </c>
-      <c r="D12" s="324" t="s">
+      <c r="D12" s="321" t="s">
         <v>220</v>
       </c>
-      <c r="E12" s="324"/>
-      <c r="F12" s="325"/>
+      <c r="E12" s="321"/>
+      <c r="F12" s="322"/>
     </row>
     <row r="13" spans="2:7" ht="26.5" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B13" s="312">
+      <c r="B13" s="335">
         <v>8</v>
       </c>
-      <c r="C13" s="313">
+      <c r="C13" s="336">
         <v>8</v>
       </c>
-      <c r="D13" s="334" t="s">
-        <v>303</v>
-      </c>
-      <c r="E13" s="334"/>
-      <c r="F13" s="335"/>
+      <c r="D13" s="333" t="s">
+        <v>302</v>
+      </c>
+      <c r="E13" s="333"/>
+      <c r="F13" s="334"/>
     </row>
     <row r="14" spans="2:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="C14" s="209"/>
-      <c r="D14" s="328" t="s">
-        <v>326</v>
-      </c>
-      <c r="E14" s="329"/>
-      <c r="F14" s="330"/>
+      <c r="D14" s="327" t="s">
+        <v>325</v>
+      </c>
+      <c r="E14" s="328"/>
+      <c r="F14" s="329"/>
       <c r="G14" s="106"/>
     </row>
     <row r="15" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.6">
       <c r="C15" s="209"/>
-      <c r="D15" s="331" t="s">
-        <v>327</v>
-      </c>
-      <c r="E15" s="332"/>
-      <c r="F15" s="333"/>
+      <c r="D15" s="330" t="s">
+        <v>326</v>
+      </c>
+      <c r="E15" s="331"/>
+      <c r="F15" s="332"/>
     </row>
     <row r="16" spans="2:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="C16" s="1"/>
@@ -6514,14 +6497,14 @@
       <c r="B1" s="9"/>
     </row>
     <row r="2" spans="2:10" ht="19" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="364" t="s">
-        <v>304</v>
-      </c>
-      <c r="C2" s="365"/>
+      <c r="B2" s="367" t="s">
+        <v>303</v>
+      </c>
+      <c r="C2" s="368"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B3" s="192" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C3" s="193" t="s">
         <v>139</v>
@@ -6529,7 +6512,7 @@
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B4" s="80" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C4" s="155" t="s">
         <v>140</v>
@@ -6545,7 +6528,7 @@
     </row>
     <row r="6" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="11" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="J11" s="304"/>
+      <c r="J11" s="303"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6563,7 +6546,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.7265625" customWidth="1"/>
@@ -6588,14 +6571,14 @@
       <c r="A2" s="160">
         <v>600</v>
       </c>
-      <c r="B2" s="336" t="s">
+      <c r="B2" s="339" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="337"/>
-      <c r="D2" s="337"/>
-      <c r="E2" s="337"/>
-      <c r="F2" s="337"/>
-      <c r="G2" s="338"/>
+      <c r="C2" s="340"/>
+      <c r="D2" s="340"/>
+      <c r="E2" s="340"/>
+      <c r="F2" s="340"/>
+      <c r="G2" s="341"/>
       <c r="H2" s="46"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
@@ -6615,7 +6598,7 @@
         <v>10</v>
       </c>
       <c r="F3" s="49" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G3" s="49" t="s">
         <v>11</v>
@@ -6628,6 +6611,9 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="160">
+        <v>1500</v>
+      </c>
       <c r="B4" s="51">
         <v>45139</v>
       </c>
@@ -7177,67 +7163,67 @@
       </c>
     </row>
     <row r="28" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="254">
+      <c r="B28" s="253">
         <v>45870</v>
       </c>
-      <c r="C28" s="255">
+      <c r="C28" s="254">
         <v>69854.77</v>
       </c>
-      <c r="D28" s="255">
+      <c r="D28" s="254">
         <v>149.4</v>
       </c>
-      <c r="E28" s="255">
+      <c r="E28" s="254">
         <v>28600</v>
       </c>
-      <c r="F28" s="257"/>
-      <c r="G28" s="255">
+      <c r="F28" s="256"/>
+      <c r="G28" s="254">
         <v>12368</v>
       </c>
       <c r="H28" s="207">
         <f>(C28+D28+E28+F28-G28)</f>
         <v>86236.17</v>
       </c>
-      <c r="I28" s="339"/>
-      <c r="J28" s="340"/>
-      <c r="K28" s="340"/>
-      <c r="L28" s="340"/>
+      <c r="I28" s="342"/>
+      <c r="J28" s="343"/>
+      <c r="K28" s="343"/>
+      <c r="L28" s="343"/>
     </row>
     <row r="29" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="254">
+      <c r="B29" s="253">
         <v>45901</v>
       </c>
-      <c r="C29" s="255">
+      <c r="C29" s="254">
         <v>86236.37</v>
       </c>
-      <c r="D29" s="255">
+      <c r="D29" s="254">
         <v>-309.81</v>
       </c>
-      <c r="E29" s="255">
+      <c r="E29" s="254">
         <v>30450</v>
       </c>
-      <c r="F29" s="257"/>
-      <c r="G29" s="255">
+      <c r="F29" s="256"/>
+      <c r="G29" s="254">
         <v>12994</v>
       </c>
-      <c r="H29" s="258">
+      <c r="H29" s="257">
         <v>102782.56</v>
       </c>
     </row>
     <row r="30" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="254">
+      <c r="B30" s="253">
         <v>45931</v>
       </c>
-      <c r="C30" s="255">
+      <c r="C30" s="254">
         <v>102782.56</v>
       </c>
-      <c r="D30" s="255">
+      <c r="D30" s="254">
         <v>-877.8</v>
       </c>
-      <c r="E30" s="255">
+      <c r="E30" s="254">
         <v>28700</v>
       </c>
-      <c r="F30" s="257"/>
-      <c r="G30" s="255">
+      <c r="F30" s="256"/>
+      <c r="G30" s="254">
         <v>58094</v>
       </c>
       <c r="H30" s="207">
@@ -7246,41 +7232,41 @@
       </c>
     </row>
     <row r="31" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="254">
+      <c r="B31" s="253">
         <v>45962</v>
       </c>
-      <c r="C31" s="255">
+      <c r="C31" s="254">
         <v>72510.759999999995</v>
       </c>
-      <c r="D31" s="255">
+      <c r="D31" s="254">
         <v>-37.799999999999997</v>
       </c>
-      <c r="E31" s="255">
+      <c r="E31" s="254">
         <v>27650</v>
       </c>
-      <c r="F31" s="257"/>
-      <c r="G31" s="255">
+      <c r="F31" s="256"/>
+      <c r="G31" s="254">
         <v>13064</v>
       </c>
-      <c r="H31" s="258">
+      <c r="H31" s="257">
         <v>86458.96</v>
       </c>
     </row>
     <row r="32" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="254">
+      <c r="B32" s="253">
         <v>45992</v>
       </c>
-      <c r="C32" s="255">
+      <c r="C32" s="254">
         <v>86458.96</v>
       </c>
-      <c r="D32" s="255">
+      <c r="D32" s="254">
         <v>-67.8</v>
       </c>
-      <c r="E32" s="255">
+      <c r="E32" s="254">
         <v>28050</v>
       </c>
-      <c r="F32" s="257"/>
-      <c r="G32" s="255">
+      <c r="F32" s="256"/>
+      <c r="G32" s="254">
         <v>14354</v>
       </c>
       <c r="H32" s="207">
@@ -7288,84 +7274,84 @@
         <v>100087.16</v>
       </c>
     </row>
-    <row r="33" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="254">
+    <row r="33" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B33" s="253">
         <v>46023</v>
       </c>
-      <c r="C33" s="255">
+      <c r="C33" s="254">
         <v>100087.16</v>
       </c>
-      <c r="D33" s="255">
+      <c r="D33" s="254">
         <v>-37.799999999999997</v>
       </c>
-      <c r="E33" s="255">
+      <c r="E33" s="254">
         <v>30250</v>
       </c>
-      <c r="F33" s="257"/>
-      <c r="G33" s="255">
+      <c r="F33" s="256"/>
+      <c r="G33" s="254">
         <v>9449</v>
       </c>
-      <c r="H33" s="258">
+      <c r="H33" s="257">
         <v>119650.36</v>
       </c>
     </row>
-    <row r="34" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="254">
+    <row r="34" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B34" s="253">
         <v>46054</v>
       </c>
-      <c r="C34" s="255">
+      <c r="C34" s="254">
         <v>119650.36</v>
       </c>
-      <c r="D34" s="255">
+      <c r="D34" s="254">
         <v>-58</v>
       </c>
-      <c r="E34" s="255">
+      <c r="E34" s="254">
         <v>27650</v>
       </c>
-      <c r="F34" s="257"/>
-      <c r="G34" s="255">
+      <c r="F34" s="256"/>
+      <c r="G34" s="254">
         <v>9997</v>
       </c>
-      <c r="H34" s="258">
+      <c r="H34" s="257">
         <v>136045.35999999999</v>
       </c>
     </row>
-    <row r="35" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="254">
+    <row r="35" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B35" s="253">
         <v>46082</v>
       </c>
-      <c r="C35" s="255">
+      <c r="C35" s="254">
         <v>136045.35999999999</v>
       </c>
-      <c r="D35" s="255">
+      <c r="D35" s="254">
         <v>567.20000000000005</v>
       </c>
-      <c r="E35" s="255">
+      <c r="E35" s="254">
         <v>29600</v>
       </c>
-      <c r="F35" s="257"/>
-      <c r="G35" s="255">
+      <c r="F35" s="256"/>
+      <c r="G35" s="254">
         <v>43150</v>
       </c>
-      <c r="H35" s="258">
+      <c r="H35" s="257">
         <v>121862.56</v>
       </c>
     </row>
-    <row r="36" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="254">
+    <row r="36" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="253">
         <v>46113</v>
       </c>
-      <c r="C36" s="255">
+      <c r="C36" s="254">
         <v>121862.56</v>
       </c>
-      <c r="D36" s="255">
+      <c r="D36" s="254">
         <v>80</v>
       </c>
-      <c r="E36" s="255">
+      <c r="E36" s="254">
         <v>29500</v>
       </c>
-      <c r="F36" s="257"/>
-      <c r="G36" s="255">
+      <c r="F36" s="256"/>
+      <c r="G36" s="254">
         <v>12492</v>
       </c>
       <c r="H36" s="207">
@@ -7373,21 +7359,21 @@
         <v>138950.56</v>
       </c>
     </row>
-    <row r="37" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="254">
+    <row r="37" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B37" s="253">
         <v>46143</v>
       </c>
-      <c r="C37" s="255">
+      <c r="C37" s="254">
         <v>138950.56</v>
       </c>
-      <c r="D37" s="255">
+      <c r="D37" s="254">
         <v>-50.4</v>
       </c>
-      <c r="E37" s="255">
+      <c r="E37" s="254">
         <v>29850</v>
       </c>
-      <c r="F37" s="257"/>
-      <c r="G37" s="255">
+      <c r="F37" s="256"/>
+      <c r="G37" s="254">
         <v>11801</v>
       </c>
       <c r="H37" s="207">
@@ -7395,51 +7381,97 @@
         <v>155749.16</v>
       </c>
     </row>
-    <row r="38" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="254">
+    <row r="38" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B38" s="253">
         <v>46174</v>
       </c>
-      <c r="C38" s="255">
+      <c r="C38" s="254">
         <v>155749.16</v>
       </c>
-      <c r="D38" s="255">
+      <c r="D38" s="254">
         <v>149.6</v>
       </c>
-      <c r="E38" s="255">
+      <c r="E38" s="254">
         <v>26600</v>
       </c>
-      <c r="F38" s="257"/>
-      <c r="G38" s="255">
+      <c r="F38" s="256"/>
+      <c r="G38" s="254">
         <v>16455</v>
       </c>
       <c r="H38" s="207">
         <f>(C38+D38+E38-A3+F38-G38)</f>
         <v>164843.76</v>
       </c>
-      <c r="J38" s="311"/>
-    </row>
-    <row r="39" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B39" s="254">
+      <c r="J38" s="308"/>
+    </row>
+    <row r="39" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B39" s="253">
         <v>46204</v>
       </c>
-      <c r="C39" s="255">
+      <c r="C39" s="254">
         <v>164843.76</v>
       </c>
-      <c r="D39" s="255">
+      <c r="D39" s="254">
         <v>658</v>
       </c>
-      <c r="E39" s="255">
+      <c r="E39" s="254">
         <v>29100</v>
       </c>
-      <c r="F39" s="257"/>
-      <c r="G39" s="255">
+      <c r="F39" s="256"/>
+      <c r="G39" s="254">
         <v>11746</v>
       </c>
       <c r="H39" s="207">
         <f>(C39+D39+E39-A3+F39-G39)</f>
         <v>181655.76</v>
       </c>
-      <c r="J39" s="311"/>
+      <c r="J39" s="308"/>
+    </row>
+    <row r="40" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B40" s="253">
+        <v>46235</v>
+      </c>
+      <c r="C40" s="254">
+        <v>181655.76</v>
+      </c>
+      <c r="D40" s="254">
+        <v>-12.6</v>
+      </c>
+      <c r="E40" s="254">
+        <v>31450</v>
+      </c>
+      <c r="F40" s="256"/>
+      <c r="G40" s="254">
+        <v>17949</v>
+      </c>
+      <c r="H40" s="207">
+        <f>(C40+D40+E40+F40-G40)</f>
+        <v>195144.16</v>
+      </c>
+      <c r="K40" s="308"/>
+    </row>
+    <row r="41" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B41" s="253">
+        <v>46266</v>
+      </c>
+      <c r="C41" s="254">
+        <v>195144.16</v>
+      </c>
+      <c r="D41" s="254">
+        <v>-12.6</v>
+      </c>
+      <c r="E41" s="254">
+        <v>28800</v>
+      </c>
+      <c r="F41" s="256"/>
+      <c r="G41" s="254">
+        <v>14653</v>
+      </c>
+      <c r="H41" s="207">
+        <f>(C41+D41+E41-A4+F41-G41)</f>
+        <v>207778.56</v>
+      </c>
+      <c r="K41" s="308"/>
     </row>
   </sheetData>
   <customSheetViews>
@@ -7457,7 +7489,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <ignoredErrors>
-    <ignoredError sqref="H19 H22 H37" formula="1"/>
+    <ignoredError sqref="H19 H22 H37 H40 H27 H25" formula="1"/>
   </ignoredErrors>
   <drawing r:id="rId3"/>
   <legacyDrawing r:id="rId4"/>
@@ -7467,7 +7499,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="B1:AT61"/>
+  <dimension ref="B1:AV61"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.26953125" customWidth="1"/>
@@ -7487,25 +7519,27 @@
     <col min="32" max="32" width="7.7265625" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="8.08984375" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="22.26953125" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="28" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="22.26953125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="4.1796875" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="10.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:42" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:44" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
       <c r="E1" s="33"/>
       <c r="F1" s="33"/>
     </row>
-    <row r="2" spans="2:42" ht="19" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B2" s="341" t="s">
+    <row r="2" spans="2:44" ht="19" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B2" s="344" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="342"/>
-      <c r="D2" s="342"/>
-      <c r="E2" s="342"/>
-      <c r="F2" s="342"/>
+      <c r="C2" s="345"/>
+      <c r="D2" s="345"/>
+      <c r="E2" s="345"/>
+      <c r="F2" s="345"/>
       <c r="G2" s="31">
         <v>22000</v>
       </c>
@@ -7640,8 +7674,16 @@
         <f>SUM(AP4:AP60)</f>
         <v>29100</v>
       </c>
-    </row>
-    <row r="3" spans="2:42" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AQ2" s="211">
+        <f>SUM(AQ4:AQ60)</f>
+        <v>31450</v>
+      </c>
+      <c r="AR2" s="211">
+        <f>SUM(AR4:AR60)</f>
+        <v>28800</v>
+      </c>
+    </row>
+    <row r="3" spans="2:44" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B3" s="28" t="s">
         <v>14</v>
       </c>
@@ -7765,8 +7807,14 @@
       <c r="AP3" s="212">
         <v>46204</v>
       </c>
-    </row>
-    <row r="4" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="AQ3" s="212">
+        <v>46235</v>
+      </c>
+      <c r="AR3" s="212">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="4" spans="2:44" x14ac:dyDescent="0.35">
       <c r="B4" s="11">
         <v>1</v>
       </c>
@@ -7886,8 +7934,14 @@
       <c r="AP4" s="216">
         <v>600</v>
       </c>
-    </row>
-    <row r="5" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="AQ4" s="216">
+        <v>600</v>
+      </c>
+      <c r="AR4" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="5" spans="2:44" x14ac:dyDescent="0.35">
       <c r="B5" s="16">
         <v>2</v>
       </c>
@@ -8010,8 +8064,14 @@
       <c r="AP5" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="6" spans="2:42" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AQ5" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR5" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="6" spans="2:44" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B6" s="19">
         <v>3</v>
       </c>
@@ -8115,8 +8175,14 @@
       <c r="AP6" s="223">
         <v>600</v>
       </c>
-    </row>
-    <row r="7" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="AQ6" s="223">
+        <v>600</v>
+      </c>
+      <c r="AR6" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="7" spans="2:44" x14ac:dyDescent="0.35">
       <c r="B7" s="11">
         <v>4</v>
       </c>
@@ -8236,8 +8302,14 @@
       <c r="AP7" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="8" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="AQ7" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR7" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="8" spans="2:44" x14ac:dyDescent="0.35">
       <c r="B8" s="16">
         <v>5</v>
       </c>
@@ -8359,8 +8431,14 @@
       <c r="AP8" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="9" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="AQ8" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR8" s="220">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="9" spans="2:44" x14ac:dyDescent="0.35">
       <c r="B9" s="16">
         <v>6</v>
       </c>
@@ -8368,7 +8446,7 @@
         <v>31</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>229</v>
+        <v>401</v>
       </c>
       <c r="E9" s="14"/>
       <c r="F9" s="18" t="s">
@@ -8478,8 +8556,14 @@
       <c r="AP9" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="10" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="AQ9" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR9" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="10" spans="2:44" x14ac:dyDescent="0.35">
       <c r="B10" s="16">
         <v>7</v>
       </c>
@@ -8487,7 +8571,7 @@
         <v>32</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>33</v>
+        <v>400</v>
       </c>
       <c r="E10" s="14"/>
       <c r="F10" s="18" t="s">
@@ -8599,8 +8683,14 @@
       <c r="AP10" s="224" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="11" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="AQ10" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR10" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="11" spans="2:44" x14ac:dyDescent="0.35">
       <c r="B11" s="16">
         <v>8</v>
       </c>
@@ -8722,8 +8812,14 @@
       <c r="AP11" s="224" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="12" spans="2:42" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AQ11" s="224" t="s">
+        <v>25</v>
+      </c>
+      <c r="AR11" s="224" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="2:44" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B12" s="19">
         <v>9</v>
       </c>
@@ -8845,8 +8941,14 @@
       <c r="AP12" s="226">
         <v>600</v>
       </c>
-    </row>
-    <row r="13" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="AQ12" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR12" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="13" spans="2:44" x14ac:dyDescent="0.35">
       <c r="B13" s="11">
         <v>10</v>
       </c>
@@ -8962,8 +9064,12 @@
       <c r="AP13" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="14" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="AQ13" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR13" s="306"/>
+    </row>
+    <row r="14" spans="2:44" x14ac:dyDescent="0.35">
       <c r="B14" s="16">
         <v>11</v>
       </c>
@@ -9081,8 +9187,14 @@
       <c r="AP14" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="15" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="AQ14" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR14" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="15" spans="2:44" x14ac:dyDescent="0.35">
       <c r="B15" s="16">
         <v>12</v>
       </c>
@@ -9202,8 +9314,14 @@
       <c r="AP15" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="16" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="AQ15" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR15" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="16" spans="2:44" x14ac:dyDescent="0.35">
       <c r="B16" s="16">
         <v>13</v>
       </c>
@@ -9323,8 +9441,14 @@
       <c r="AP16" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="17" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="AQ16" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR16" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="17" spans="2:48" x14ac:dyDescent="0.35">
       <c r="B17" s="16">
         <v>14</v>
       </c>
@@ -9444,8 +9568,14 @@
       <c r="AP17" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="18" spans="2:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AQ17" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR17" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="18" spans="2:48" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B18" s="19">
         <v>15</v>
       </c>
@@ -9453,7 +9583,7 @@
         <v>50</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E18" s="21">
         <v>9929901032</v>
@@ -9561,10 +9691,20 @@
       <c r="AN18" s="220" t="s">
         <v>217</v>
       </c>
-      <c r="AO18" s="308"/>
-      <c r="AP18" s="308"/>
-    </row>
-    <row r="19" spans="2:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AO18" s="220" t="s">
+        <v>217</v>
+      </c>
+      <c r="AP18" s="220" t="s">
+        <v>217</v>
+      </c>
+      <c r="AQ18" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR18" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="19" spans="2:48" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="11">
         <v>16</v>
       </c>
@@ -9684,8 +9824,14 @@
       <c r="AP19" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="20" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="AQ19" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR19" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="20" spans="2:48" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B20" s="16">
         <v>17</v>
       </c>
@@ -9803,8 +9949,14 @@
       <c r="AP20" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="21" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="AQ20" s="229" t="s">
+        <v>25</v>
+      </c>
+      <c r="AR20" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="21" spans="2:48" x14ac:dyDescent="0.35">
       <c r="B21" s="16">
         <v>18</v>
       </c>
@@ -9922,8 +10074,14 @@
       <c r="AP21" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="22" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="AQ21" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR21" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="22" spans="2:48" x14ac:dyDescent="0.35">
       <c r="B22" s="16">
         <v>19</v>
       </c>
@@ -10039,8 +10197,14 @@
       <c r="AP22" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="23" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="AQ22" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR22" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="23" spans="2:48" x14ac:dyDescent="0.35">
       <c r="B23" s="16">
         <v>20</v>
       </c>
@@ -10162,8 +10326,14 @@
       <c r="AP23" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="24" spans="2:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AQ23" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR23" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="24" spans="2:48" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B24" s="19">
         <v>21</v>
       </c>
@@ -10285,8 +10455,14 @@
       <c r="AP24" s="226">
         <v>600</v>
       </c>
-    </row>
-    <row r="25" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="AQ24" s="226">
+        <v>600</v>
+      </c>
+      <c r="AR24" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="25" spans="2:48" x14ac:dyDescent="0.35">
       <c r="B25" s="11">
         <v>22</v>
       </c>
@@ -10408,8 +10584,14 @@
       <c r="AP25" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="26" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="AQ25" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR25" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="26" spans="2:48" x14ac:dyDescent="0.35">
       <c r="B26" s="16">
         <v>23</v>
       </c>
@@ -10531,8 +10713,14 @@
       <c r="AP26" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="27" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="AQ26" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR26" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="27" spans="2:48" x14ac:dyDescent="0.35">
       <c r="B27" s="16">
         <v>24</v>
       </c>
@@ -10635,13 +10823,17 @@
       <c r="AM27" s="233">
         <v>800</v>
       </c>
-      <c r="AN27" s="234"/>
-      <c r="AO27" s="308"/>
+      <c r="AN27" s="311"/>
+      <c r="AO27" s="247"/>
       <c r="AP27" s="220">
         <v>1200</v>
       </c>
-    </row>
-    <row r="28" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="AQ27" s="220">
+        <v>1350</v>
+      </c>
+      <c r="AR27" s="306"/>
+    </row>
+    <row r="28" spans="2:48" x14ac:dyDescent="0.35">
       <c r="B28" s="16">
         <v>25</v>
       </c>
@@ -10747,10 +10939,10 @@
       <c r="AL28" s="219">
         <v>600</v>
       </c>
-      <c r="AM28" s="235">
-        <v>600</v>
-      </c>
-      <c r="AN28" s="235">
+      <c r="AM28" s="234">
+        <v>600</v>
+      </c>
+      <c r="AN28" s="234">
         <v>600</v>
       </c>
       <c r="AO28" s="220">
@@ -10759,8 +10951,14 @@
       <c r="AP28" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="29" spans="2:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AQ28" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR28" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="29" spans="2:48" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B29" s="16">
         <v>26</v>
       </c>
@@ -10866,10 +11064,10 @@
       <c r="AL29" s="219">
         <v>600</v>
       </c>
-      <c r="AM29" s="235">
-        <v>600</v>
-      </c>
-      <c r="AN29" s="235">
+      <c r="AM29" s="234">
+        <v>600</v>
+      </c>
+      <c r="AN29" s="234">
         <v>600</v>
       </c>
       <c r="AO29" s="220">
@@ -10878,8 +11076,14 @@
       <c r="AP29" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="30" spans="2:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AQ29" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR29" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="30" spans="2:48" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B30" s="19">
         <v>27</v>
       </c>
@@ -10933,30 +11137,36 @@
       <c r="AJ30" s="221">
         <v>600</v>
       </c>
-      <c r="AK30" s="236"/>
-      <c r="AL30" s="237"/>
-      <c r="AM30" s="238"/>
-      <c r="AN30" s="238"/>
-      <c r="AO30" s="238">
+      <c r="AK30" s="235"/>
+      <c r="AL30" s="236"/>
+      <c r="AM30" s="237"/>
+      <c r="AN30" s="237"/>
+      <c r="AO30" s="237">
         <v>200</v>
       </c>
       <c r="AP30" s="220">
         <v>650</v>
       </c>
-      <c r="AQ30" s="176" t="s">
-        <v>286</v>
-      </c>
-      <c r="AR30" s="176" t="s">
-        <v>302</v>
+      <c r="AQ30" s="314">
+        <v>600</v>
+      </c>
+      <c r="AR30" s="314">
+        <v>600</v>
       </c>
       <c r="AS30" s="176" t="s">
-        <v>389</v>
+        <v>285</v>
       </c>
       <c r="AT30" s="176" t="s">
+        <v>301</v>
+      </c>
+      <c r="AU30" s="176" t="s">
+        <v>388</v>
+      </c>
+      <c r="AV30" s="176" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="31" spans="2:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:48" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B31" s="11">
         <v>28</v>
       </c>
@@ -11067,7 +11277,7 @@
       <c r="AM31" s="219">
         <v>600</v>
       </c>
-      <c r="AN31" s="235">
+      <c r="AN31" s="234">
         <v>600</v>
       </c>
       <c r="AO31" s="220">
@@ -11076,20 +11286,26 @@
       <c r="AP31" s="220">
         <v>600</v>
       </c>
-      <c r="AQ31" s="305" t="s">
-        <v>390</v>
-      </c>
-      <c r="AR31" s="119">
-        <v>700</v>
-      </c>
-      <c r="AS31" s="305" t="s">
-        <v>391</v>
-      </c>
-      <c r="AT31" s="309" t="s">
+      <c r="AQ31" s="314">
+        <v>600</v>
+      </c>
+      <c r="AR31" s="220">
+        <v>600</v>
+      </c>
+      <c r="AS31" s="119" t="s">
+        <v>405</v>
+      </c>
+      <c r="AT31" s="119">
+        <v>650</v>
+      </c>
+      <c r="AU31" s="119" t="s">
+        <v>406</v>
+      </c>
+      <c r="AV31" s="119" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="32" spans="2:46" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:48" x14ac:dyDescent="0.35">
       <c r="B32" s="16">
         <v>29</v>
       </c>
@@ -11202,7 +11418,7 @@
       <c r="AM32" s="215">
         <v>600</v>
       </c>
-      <c r="AN32" s="239">
+      <c r="AN32" s="238">
         <v>600</v>
       </c>
       <c r="AO32" s="220">
@@ -11211,20 +11427,26 @@
       <c r="AP32" s="220">
         <v>600</v>
       </c>
-      <c r="AQ32" s="119" t="s">
-        <v>397</v>
-      </c>
-      <c r="AR32" s="119">
-        <v>50</v>
+      <c r="AQ32" s="314">
+        <v>600</v>
+      </c>
+      <c r="AR32" s="220">
+        <v>600</v>
       </c>
       <c r="AS32" s="119" t="s">
-        <v>394</v>
-      </c>
-      <c r="AT32" s="119" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="33" spans="2:46" x14ac:dyDescent="0.35">
+        <v>407</v>
+      </c>
+      <c r="AT32" s="119">
+        <v>650</v>
+      </c>
+      <c r="AU32" s="119" t="s">
+        <v>408</v>
+      </c>
+      <c r="AV32" s="119" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="33" spans="2:48" x14ac:dyDescent="0.35">
       <c r="B33" s="16">
         <v>30</v>
       </c>
@@ -11330,10 +11552,10 @@
       <c r="AL33" s="219">
         <v>600</v>
       </c>
-      <c r="AM33" s="235">
-        <v>600</v>
-      </c>
-      <c r="AN33" s="240">
+      <c r="AM33" s="234">
+        <v>600</v>
+      </c>
+      <c r="AN33" s="239">
         <v>600</v>
       </c>
       <c r="AO33" s="220">
@@ -11342,20 +11564,26 @@
       <c r="AP33" s="220">
         <v>600</v>
       </c>
-      <c r="AQ33" s="119" t="s">
-        <v>398</v>
-      </c>
-      <c r="AR33" s="119">
-        <v>600</v>
-      </c>
-      <c r="AS33" s="119" t="s">
-        <v>399</v>
-      </c>
-      <c r="AT33" s="366" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="34" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="AQ33" s="314">
+        <v>600</v>
+      </c>
+      <c r="AR33" s="220">
+        <v>600</v>
+      </c>
+      <c r="AS33" s="309" t="s">
+        <v>392</v>
+      </c>
+      <c r="AT33" s="310">
+        <v>650</v>
+      </c>
+      <c r="AU33" s="309" t="s">
+        <v>393</v>
+      </c>
+      <c r="AV33" s="309" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="34" spans="2:48" x14ac:dyDescent="0.35">
       <c r="B34" s="16">
         <v>31</v>
       </c>
@@ -11449,10 +11677,10 @@
       <c r="AL34" s="219">
         <v>600</v>
       </c>
-      <c r="AM34" s="235">
-        <v>600</v>
-      </c>
-      <c r="AN34" s="240">
+      <c r="AM34" s="234">
+        <v>600</v>
+      </c>
+      <c r="AN34" s="239">
         <v>600</v>
       </c>
       <c r="AO34" s="220">
@@ -11461,20 +11689,26 @@
       <c r="AP34" s="220">
         <v>600</v>
       </c>
-      <c r="AQ34" s="119" t="s">
-        <v>400</v>
-      </c>
-      <c r="AR34" s="119">
-        <v>1350</v>
+      <c r="AQ34" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR34" s="220">
+        <v>600</v>
       </c>
       <c r="AS34" s="119" t="s">
-        <v>401</v>
-      </c>
-      <c r="AT34" s="119" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="35" spans="2:46" x14ac:dyDescent="0.35">
+        <v>394</v>
+      </c>
+      <c r="AT34" s="119">
+        <v>650</v>
+      </c>
+      <c r="AU34" s="119" t="s">
+        <v>395</v>
+      </c>
+      <c r="AV34" s="119" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="35" spans="2:48" x14ac:dyDescent="0.35">
       <c r="B35" s="16">
         <v>32</v>
       </c>
@@ -11584,7 +11818,7 @@
       <c r="AL35" s="219">
         <v>600</v>
       </c>
-      <c r="AM35" s="241" t="s">
+      <c r="AM35" s="240" t="s">
         <v>25</v>
       </c>
       <c r="AN35" s="224" t="s">
@@ -11596,20 +11830,18 @@
       <c r="AP35" s="224" t="s">
         <v>25</v>
       </c>
-      <c r="AQ35" s="119" t="s">
-        <v>402</v>
-      </c>
-      <c r="AR35" s="119">
-        <v>1350</v>
-      </c>
-      <c r="AS35" s="119" t="s">
-        <v>403</v>
-      </c>
-      <c r="AT35" s="119" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="36" spans="2:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AQ35" s="224" t="s">
+        <v>25</v>
+      </c>
+      <c r="AR35" s="224" t="s">
+        <v>25</v>
+      </c>
+      <c r="AS35" s="313"/>
+      <c r="AT35" s="119"/>
+      <c r="AU35" s="119"/>
+      <c r="AV35" s="313"/>
+    </row>
+    <row r="36" spans="2:48" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B36" s="19">
         <v>33</v>
       </c>
@@ -11727,8 +11959,14 @@
       <c r="AP36" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="37" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="AQ36" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR36" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="37" spans="2:48" x14ac:dyDescent="0.35">
       <c r="B37" s="11">
         <v>34</v>
       </c>
@@ -11778,14 +12016,16 @@
       <c r="AH37" s="224"/>
       <c r="AI37" s="224"/>
       <c r="AJ37" s="224"/>
-      <c r="AK37" s="242"/>
-      <c r="AL37" s="243"/>
-      <c r="AM37" s="243"/>
-      <c r="AN37" s="243"/>
-      <c r="AO37" s="243"/>
-      <c r="AP37" s="243"/>
-    </row>
-    <row r="38" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="AK37" s="241"/>
+      <c r="AL37" s="242"/>
+      <c r="AM37" s="242"/>
+      <c r="AN37" s="242"/>
+      <c r="AO37" s="242"/>
+      <c r="AP37" s="242"/>
+      <c r="AQ37" s="242"/>
+      <c r="AR37" s="242"/>
+    </row>
+    <row r="38" spans="2:48" x14ac:dyDescent="0.35">
       <c r="B38" s="16">
         <v>35</v>
       </c>
@@ -11907,8 +12147,14 @@
       <c r="AP38" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="39" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="AQ38" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR38" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="39" spans="2:48" x14ac:dyDescent="0.35">
       <c r="B39" s="16">
         <v>36</v>
       </c>
@@ -11958,14 +12204,16 @@
       <c r="AH39" s="224"/>
       <c r="AI39" s="224"/>
       <c r="AJ39" s="224"/>
-      <c r="AK39" s="242"/>
-      <c r="AL39" s="243"/>
-      <c r="AM39" s="243"/>
-      <c r="AN39" s="243"/>
-      <c r="AO39" s="243"/>
-      <c r="AP39" s="243"/>
-    </row>
-    <row r="40" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="AK39" s="241"/>
+      <c r="AL39" s="242"/>
+      <c r="AM39" s="242"/>
+      <c r="AN39" s="242"/>
+      <c r="AO39" s="242"/>
+      <c r="AP39" s="242"/>
+      <c r="AQ39" s="242"/>
+      <c r="AR39" s="242"/>
+    </row>
+    <row r="40" spans="2:48" x14ac:dyDescent="0.35">
       <c r="B40" s="16">
         <v>37</v>
       </c>
@@ -12087,8 +12335,14 @@
       <c r="AP40" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="41" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="AQ40" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR40" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="41" spans="2:48" x14ac:dyDescent="0.35">
       <c r="B41" s="16">
         <v>38</v>
       </c>
@@ -12138,18 +12392,20 @@
       <c r="AH41" s="224"/>
       <c r="AI41" s="224"/>
       <c r="AJ41" s="224"/>
-      <c r="AK41" s="242"/>
-      <c r="AL41" s="243"/>
-      <c r="AM41" s="243" t="s">
-        <v>329</v>
-      </c>
-      <c r="AN41" s="244">
+      <c r="AK41" s="241"/>
+      <c r="AL41" s="242"/>
+      <c r="AM41" s="242" t="s">
+        <v>328</v>
+      </c>
+      <c r="AN41" s="243">
         <v>200</v>
       </c>
-      <c r="AO41" s="243"/>
-      <c r="AP41" s="243"/>
-    </row>
-    <row r="42" spans="2:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AO41" s="242"/>
+      <c r="AP41" s="242"/>
+      <c r="AQ41" s="242"/>
+      <c r="AR41" s="242"/>
+    </row>
+    <row r="42" spans="2:48" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B42" s="19">
         <v>39</v>
       </c>
@@ -12235,7 +12491,7 @@
       <c r="AD42" s="105">
         <v>600</v>
       </c>
-      <c r="AE42" s="245" t="s">
+      <c r="AE42" s="244" t="s">
         <v>217</v>
       </c>
       <c r="AF42" s="221">
@@ -12271,8 +12527,14 @@
       <c r="AP42" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="43" spans="2:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AQ42" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR42" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="43" spans="2:48" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B43" s="11">
         <v>40</v>
       </c>
@@ -12388,12 +12650,18 @@
       <c r="AN43" s="219">
         <v>800</v>
       </c>
-      <c r="AO43" s="248"/>
+      <c r="AO43" s="247"/>
       <c r="AP43" s="220">
         <v>1250</v>
       </c>
-    </row>
-    <row r="44" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="AQ43" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR43" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="44" spans="2:48" x14ac:dyDescent="0.35">
       <c r="B44" s="16">
         <v>41</v>
       </c>
@@ -12507,8 +12775,14 @@
       <c r="AP44" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="45" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="AQ44" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR44" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="45" spans="2:48" x14ac:dyDescent="0.35">
       <c r="B45" s="16">
         <v>42</v>
       </c>
@@ -12617,7 +12891,7 @@
       <c r="AM45" s="219">
         <v>600</v>
       </c>
-      <c r="AN45" s="246">
+      <c r="AN45" s="245">
         <v>850</v>
       </c>
       <c r="AO45" s="220">
@@ -12626,8 +12900,14 @@
       <c r="AP45" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="46" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="AQ45" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR45" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="46" spans="2:48" x14ac:dyDescent="0.35">
       <c r="B46" s="16">
         <v>43</v>
       </c>
@@ -12749,8 +13029,14 @@
       <c r="AP46" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="47" spans="2:46" x14ac:dyDescent="0.35">
+      <c r="AQ46" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR46" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="47" spans="2:48" x14ac:dyDescent="0.35">
       <c r="B47" s="16">
         <v>44</v>
       </c>
@@ -12758,7 +13044,7 @@
         <v>109</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E47" s="14"/>
       <c r="F47" s="23"/>
@@ -12868,8 +13154,14 @@
       <c r="AP47" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="48" spans="2:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AQ47" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR47" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="48" spans="2:48" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B48" s="19">
         <v>45</v>
       </c>
@@ -12989,8 +13281,14 @@
       <c r="AP48" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="49" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="AQ48" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR48" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="49" spans="2:46" x14ac:dyDescent="0.35">
       <c r="B49" s="11">
         <v>46</v>
       </c>
@@ -13110,8 +13408,14 @@
       <c r="AP49" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="50" spans="2:42" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AQ49" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR49" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="50" spans="2:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B50" s="16">
         <v>47</v>
       </c>
@@ -13229,8 +13533,14 @@
       <c r="AP50" s="220">
         <v>800</v>
       </c>
-    </row>
-    <row r="51" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="AQ50" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR50" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="51" spans="2:46" x14ac:dyDescent="0.35">
       <c r="B51" s="16">
         <v>48</v>
       </c>
@@ -13238,7 +13548,7 @@
         <v>117</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E51" s="14"/>
       <c r="F51" s="23"/>
@@ -13350,8 +13660,14 @@
       <c r="AP51" s="224" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="52" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="AQ51" s="224" t="s">
+        <v>25</v>
+      </c>
+      <c r="AR51" s="224" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="2:46" x14ac:dyDescent="0.35">
       <c r="B52" s="16">
         <v>49</v>
       </c>
@@ -13386,13 +13702,13 @@
         <v>500</v>
       </c>
       <c r="O52" s="105" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P52" s="14">
         <v>1050</v>
       </c>
       <c r="Q52" s="105" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="R52" s="14">
         <v>1050</v>
@@ -13401,25 +13717,25 @@
         <v>500</v>
       </c>
       <c r="T52" s="124" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="U52" s="124" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="V52" s="124">
         <v>1650</v>
       </c>
       <c r="W52" s="124" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="X52" s="124" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Y52" s="105">
         <v>1800</v>
       </c>
       <c r="Z52" s="124" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AA52" s="108">
         <v>1300</v>
@@ -13449,20 +13765,24 @@
         <v>650</v>
       </c>
       <c r="AJ52" s="231"/>
-      <c r="AK52" s="247">
+      <c r="AK52" s="246">
         <v>1250</v>
       </c>
-      <c r="AL52" s="248"/>
-      <c r="AM52" s="249">
+      <c r="AL52" s="247"/>
+      <c r="AM52" s="248">
         <v>1250</v>
       </c>
       <c r="AN52" s="219">
         <v>600</v>
       </c>
-      <c r="AO52" s="308"/>
-      <c r="AP52" s="308"/>
-    </row>
-    <row r="53" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="AO52" s="247"/>
+      <c r="AP52" s="247"/>
+      <c r="AQ52" s="247">
+        <v>2000</v>
+      </c>
+      <c r="AR52" s="306"/>
+    </row>
+    <row r="53" spans="2:46" x14ac:dyDescent="0.35">
       <c r="B53" s="16">
         <v>50</v>
       </c>
@@ -13493,10 +13813,10 @@
       <c r="M53" s="14">
         <v>500</v>
       </c>
-      <c r="N53" s="343" t="s">
+      <c r="N53" s="346" t="s">
         <v>26</v>
       </c>
-      <c r="O53" s="344"/>
+      <c r="O53" s="347"/>
       <c r="P53" s="119"/>
       <c r="Q53" s="119">
         <v>500</v>
@@ -13567,15 +13887,23 @@
       <c r="AM53" s="219">
         <v>600</v>
       </c>
-      <c r="AN53" s="246">
+      <c r="AN53" s="245">
         <v>800</v>
       </c>
       <c r="AO53" s="224" t="s">
         <v>25</v>
       </c>
-      <c r="AP53" s="224"/>
-    </row>
-    <row r="54" spans="2:42" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AP53" s="224" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ53" s="224" t="s">
+        <v>25</v>
+      </c>
+      <c r="AR53" s="224" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" spans="2:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B54" s="19">
         <v>51</v>
       </c>
@@ -13693,8 +14021,14 @@
       <c r="AP54" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="55" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="AQ54" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR54" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="55" spans="2:46" x14ac:dyDescent="0.35">
       <c r="B55" s="11">
         <v>52</v>
       </c>
@@ -13702,7 +14036,7 @@
         <v>125</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E55" s="13"/>
       <c r="F55" s="26" t="s">
@@ -13775,10 +14109,10 @@
       <c r="AG55" s="224" t="s">
         <v>25</v>
       </c>
-      <c r="AH55" s="250">
+      <c r="AH55" s="249">
         <v>650</v>
       </c>
-      <c r="AI55" s="251">
+      <c r="AI55" s="250">
         <v>600</v>
       </c>
       <c r="AJ55" s="217">
@@ -13802,8 +14136,15 @@
       <c r="AP55" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="56" spans="2:42" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AQ55" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR55" s="220">
+        <v>600</v>
+      </c>
+      <c r="AT55" s="312"/>
+    </row>
+    <row r="56" spans="2:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B56" s="16">
         <v>53</v>
       </c>
@@ -13885,8 +14226,8 @@
       <c r="AD56" s="104">
         <v>1250</v>
       </c>
-      <c r="AE56" s="252" t="s">
-        <v>328</v>
+      <c r="AE56" s="251" t="s">
+        <v>327</v>
       </c>
       <c r="AF56" s="217">
         <v>550</v>
@@ -13921,8 +14262,15 @@
       <c r="AP56" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="57" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="AQ56" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR56" s="220">
+        <v>600</v>
+      </c>
+      <c r="AT56" s="312"/>
+    </row>
+    <row r="57" spans="2:46" x14ac:dyDescent="0.35">
       <c r="B57" s="16">
         <v>54</v>
       </c>
@@ -13930,7 +14278,7 @@
         <v>129</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E57" s="14"/>
       <c r="F57" s="18" t="s">
@@ -14040,8 +14388,15 @@
       <c r="AP57" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="58" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="AQ57" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR57" s="220">
+        <v>600</v>
+      </c>
+      <c r="AT57" s="310"/>
+    </row>
+    <row r="58" spans="2:46" x14ac:dyDescent="0.35">
       <c r="B58" s="16">
         <v>55</v>
       </c>
@@ -14049,7 +14404,7 @@
         <v>130</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E58" s="14"/>
       <c r="F58" s="18" t="s">
@@ -14123,32 +14478,39 @@
       <c r="AD58" s="108">
         <v>1350</v>
       </c>
-      <c r="AE58" s="253"/>
+      <c r="AE58" s="252"/>
       <c r="AF58" s="217">
         <v>1300</v>
       </c>
       <c r="AG58" s="231"/>
       <c r="AH58" s="231"/>
-      <c r="AI58" s="306">
+      <c r="AI58" s="304">
         <v>1000</v>
       </c>
       <c r="AJ58" s="233">
         <v>1000</v>
       </c>
-      <c r="AK58" s="307"/>
-      <c r="AL58" s="249">
+      <c r="AK58" s="305"/>
+      <c r="AL58" s="248">
         <v>1000</v>
       </c>
-      <c r="AM58" s="249">
+      <c r="AM58" s="248">
         <v>1000</v>
       </c>
-      <c r="AN58" s="310">
+      <c r="AN58" s="307">
         <v>1350</v>
       </c>
-      <c r="AO58" s="308"/>
-      <c r="AP58" s="308"/>
-    </row>
-    <row r="59" spans="2:42" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AO58" s="247"/>
+      <c r="AP58" s="247"/>
+      <c r="AQ58" s="247">
+        <v>500</v>
+      </c>
+      <c r="AR58" s="306">
+        <v>1500</v>
+      </c>
+      <c r="AT58" s="310"/>
+    </row>
+    <row r="59" spans="2:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B59" s="16">
         <v>56</v>
       </c>
@@ -14256,14 +14618,20 @@
       <c r="AN59" s="219">
         <v>600</v>
       </c>
-      <c r="AO59" s="308">
+      <c r="AO59" s="306">
         <v>600</v>
       </c>
       <c r="AP59" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="60" spans="2:42" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AQ59" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR59" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="60" spans="2:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B60" s="19">
         <v>57</v>
       </c>
@@ -14383,8 +14751,14 @@
       <c r="AP60" s="220">
         <v>600</v>
       </c>
-    </row>
-    <row r="61" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="AQ60" s="220">
+        <v>600</v>
+      </c>
+      <c r="AR60" s="220">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="61" spans="2:46" x14ac:dyDescent="0.35">
       <c r="B61" s="10"/>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
@@ -14410,7 +14784,7 @@
       <selection pane="bottomRight" activeCell="S12" sqref="S12"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-      <autoFilter ref="C1:L61" xr:uid="{C8E50D97-1389-4EBC-9691-8F0EAB31A9C9}"/>
+      <autoFilter ref="C1:L61" xr:uid="{0000D5FB-7F7D-4270-86F7-8BABEBC30836}"/>
     </customSheetView>
   </customSheetViews>
   <mergeCells count="2">
@@ -14447,7 +14821,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="B1:N247"/>
+  <dimension ref="B1:N255"/>
   <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.26953125" customWidth="1"/>
@@ -14465,12 +14839,12 @@
       <c r="E1" s="9"/>
     </row>
     <row r="2" spans="2:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="349" t="s">
+      <c r="B2" s="352" t="s">
         <v>141</v>
       </c>
-      <c r="C2" s="350"/>
-      <c r="D2" s="350"/>
-      <c r="E2" s="351"/>
+      <c r="C2" s="353"/>
+      <c r="D2" s="353"/>
+      <c r="E2" s="354"/>
     </row>
     <row r="3" spans="2:6" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B3" s="57" t="s">
@@ -14599,10 +14973,10 @@
       </c>
     </row>
     <row r="12" spans="2:6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="345" t="s">
+      <c r="B12" s="348" t="s">
         <v>153</v>
       </c>
-      <c r="C12" s="346"/>
+      <c r="C12" s="349"/>
       <c r="D12" s="44">
         <f>SUM(D4:D11)</f>
         <v>38013</v>
@@ -14638,10 +15012,10 @@
       </c>
     </row>
     <row r="15" spans="2:6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="345" t="s">
+      <c r="B15" s="348" t="s">
         <v>153</v>
       </c>
-      <c r="C15" s="346"/>
+      <c r="C15" s="349"/>
       <c r="D15" s="44">
         <f>SUM(D13:D14)</f>
         <v>7911</v>
@@ -14784,10 +15158,10 @@
       </c>
     </row>
     <row r="25" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="347" t="s">
+      <c r="B25" s="350" t="s">
         <v>153</v>
       </c>
-      <c r="C25" s="348"/>
+      <c r="C25" s="351"/>
       <c r="D25" s="112">
         <f>SUM(D16:D24)</f>
         <v>49415.82</v>
@@ -14838,10 +15212,10 @@
       </c>
     </row>
     <row r="29" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="345" t="s">
+      <c r="B29" s="348" t="s">
         <v>153</v>
       </c>
-      <c r="C29" s="346"/>
+      <c r="C29" s="349"/>
       <c r="D29" s="115">
         <f>SUM(D26:D28)</f>
         <v>10058</v>
@@ -14938,10 +15312,10 @@
       </c>
     </row>
     <row r="36" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="345" t="s">
+      <c r="B36" s="348" t="s">
         <v>153</v>
       </c>
-      <c r="C36" s="346"/>
+      <c r="C36" s="349"/>
       <c r="D36" s="115">
         <f>SUM(D30:D35)</f>
         <v>12517</v>
@@ -14963,10 +15337,10 @@
       </c>
     </row>
     <row r="38" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="345" t="s">
+      <c r="B38" s="348" t="s">
         <v>153</v>
       </c>
-      <c r="C38" s="346"/>
+      <c r="C38" s="349"/>
       <c r="D38" s="115">
         <f>SUM(D37:D37)</f>
         <v>9059</v>
@@ -15016,10 +15390,10 @@
       </c>
     </row>
     <row r="42" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="345" t="s">
+      <c r="B42" s="348" t="s">
         <v>153</v>
       </c>
-      <c r="C42" s="346"/>
+      <c r="C42" s="349"/>
       <c r="D42" s="115">
         <f>SUM(D39:D41)</f>
         <v>11812</v>
@@ -15069,10 +15443,10 @@
       </c>
     </row>
     <row r="46" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="345" t="s">
+      <c r="B46" s="348" t="s">
         <v>153</v>
       </c>
-      <c r="C46" s="346"/>
+      <c r="C46" s="349"/>
       <c r="D46" s="115">
         <f>SUM(D43:D45)</f>
         <v>9011.5</v>
@@ -15108,10 +15482,10 @@
       </c>
     </row>
     <row r="49" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B49" s="345" t="s">
+      <c r="B49" s="348" t="s">
         <v>153</v>
       </c>
-      <c r="C49" s="346"/>
+      <c r="C49" s="349"/>
       <c r="D49" s="115">
         <f>SUM(D47:D48)</f>
         <v>12382</v>
@@ -15262,10 +15636,10 @@
       </c>
     </row>
     <row r="60" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="345" t="s">
+      <c r="B60" s="348" t="s">
         <v>153</v>
       </c>
-      <c r="C60" s="346"/>
+      <c r="C60" s="349"/>
       <c r="D60" s="122">
         <f>SUM(D50:D59)</f>
         <v>43425</v>
@@ -15329,10 +15703,10 @@
       </c>
     </row>
     <row r="65" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B65" s="345" t="s">
+      <c r="B65" s="348" t="s">
         <v>153</v>
       </c>
-      <c r="C65" s="346"/>
+      <c r="C65" s="349"/>
       <c r="D65" s="115">
         <f>SUM(D61:D64)</f>
         <v>23287</v>
@@ -15430,10 +15804,10 @@
       </c>
     </row>
     <row r="72" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="345" t="s">
+      <c r="B72" s="348" t="s">
         <v>153</v>
       </c>
-      <c r="C72" s="346"/>
+      <c r="C72" s="349"/>
       <c r="D72" s="115">
         <f>SUM(D66:D71)</f>
         <v>13393</v>
@@ -15528,15 +15902,15 @@
         <v>500</v>
       </c>
       <c r="E78" s="145" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F78" s="89"/>
     </row>
     <row r="79" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B79" s="345" t="s">
+      <c r="B79" s="348" t="s">
         <v>153</v>
       </c>
-      <c r="C79" s="346"/>
+      <c r="C79" s="349"/>
       <c r="D79" s="115">
         <f>SUM(D73:D78)</f>
         <v>10108</v>
@@ -15569,17 +15943,17 @@
         <v>555</v>
       </c>
       <c r="E81" s="65" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F81" s="89" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="82" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="345" t="s">
+      <c r="B82" s="348" t="s">
         <v>153</v>
       </c>
-      <c r="C82" s="346"/>
+      <c r="C82" s="349"/>
       <c r="D82" s="115">
         <f>SUM(D80:D81)</f>
         <v>8677</v>
@@ -15612,7 +15986,7 @@
         <v>5000</v>
       </c>
       <c r="E84" s="65" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F84" s="89" t="s">
         <v>140</v>
@@ -15629,14 +16003,14 @@
         <v>130</v>
       </c>
       <c r="E85" s="145" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="86" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="345" t="s">
+      <c r="B86" s="348" t="s">
         <v>153</v>
       </c>
-      <c r="C86" s="346"/>
+      <c r="C86" s="349"/>
       <c r="D86" s="115">
         <f>SUM(D83:D85)</f>
         <v>12995</v>
@@ -15654,7 +16028,7 @@
         <v>600</v>
       </c>
       <c r="E87" s="149" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F87" s="89"/>
     </row>
@@ -15669,7 +16043,7 @@
         <v>200</v>
       </c>
       <c r="E88" s="65" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F88" s="89"/>
     </row>
@@ -15698,7 +16072,7 @@
         <v>8366</v>
       </c>
       <c r="E90" s="145" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F90" s="89" t="s">
         <v>140</v>
@@ -15715,7 +16089,7 @@
         <v>840</v>
       </c>
       <c r="E91" s="145" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F91" s="89" t="s">
         <v>140</v>
@@ -15732,7 +16106,7 @@
         <v>1800</v>
       </c>
       <c r="E92" s="145" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="93" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15746,14 +16120,14 @@
         <v>60</v>
       </c>
       <c r="E93" s="150" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="94" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="345" t="s">
+      <c r="B94" s="348" t="s">
         <v>153</v>
       </c>
-      <c r="C94" s="346"/>
+      <c r="C94" s="349"/>
       <c r="D94" s="115">
         <f>SUM(D87:D93)</f>
         <v>20860</v>
@@ -15771,7 +16145,7 @@
         <v>470</v>
       </c>
       <c r="E95" s="149" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F95" s="89"/>
     </row>
@@ -15786,7 +16160,7 @@
         <v>10000</v>
       </c>
       <c r="E96" s="65" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F96" s="89"/>
     </row>
@@ -15801,7 +16175,7 @@
         <v>15000</v>
       </c>
       <c r="E97" s="65" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="98" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15815,7 +16189,7 @@
         <v>400</v>
       </c>
       <c r="E98" s="145" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F98" s="89"/>
     </row>
@@ -15830,7 +16204,7 @@
         <v>450</v>
       </c>
       <c r="E99" s="145" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F99" s="89"/>
     </row>
@@ -15845,7 +16219,7 @@
         <v>25000</v>
       </c>
       <c r="E100" s="145" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="101" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15859,7 +16233,7 @@
         <v>7239</v>
       </c>
       <c r="E101" s="145" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="102" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15873,7 +16247,7 @@
         <v>15000</v>
       </c>
       <c r="E102" s="151" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="103" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15887,7 +16261,7 @@
         <v>5000</v>
       </c>
       <c r="E103" s="151" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="104" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15901,7 +16275,7 @@
         <v>10000</v>
       </c>
       <c r="E104" s="151" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="105" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15915,7 +16289,7 @@
         <v>35000</v>
       </c>
       <c r="E105" s="151" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="106" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15929,7 +16303,7 @@
         <v>5000</v>
       </c>
       <c r="E106" s="151" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="107" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15943,7 +16317,7 @@
         <v>500</v>
       </c>
       <c r="E107" s="151" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="108" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15957,7 +16331,7 @@
         <v>300</v>
       </c>
       <c r="E108" s="151" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="109" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15971,7 +16345,7 @@
         <v>-7000</v>
       </c>
       <c r="E109" s="151" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="N109" s="138"/>
     </row>
@@ -15986,7 +16360,7 @@
         <v>25000</v>
       </c>
       <c r="E110" s="151" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="N110" s="138"/>
     </row>
@@ -16001,7 +16375,7 @@
         <v>300</v>
       </c>
       <c r="E111" s="151" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="112" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16015,7 +16389,7 @@
         <v>25000</v>
       </c>
       <c r="E112" s="151" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="113" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16029,7 +16403,7 @@
         <v>1000</v>
       </c>
       <c r="E113" s="151" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="114" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16043,7 +16417,7 @@
         <v>25000</v>
       </c>
       <c r="E114" s="151" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="115" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16057,7 +16431,7 @@
         <v>300</v>
       </c>
       <c r="E115" s="151" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="116" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16071,7 +16445,7 @@
         <v>5100</v>
       </c>
       <c r="E116" s="151" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="117" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16085,7 +16459,7 @@
         <v>2457</v>
       </c>
       <c r="E117" s="151" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F117" s="89" t="s">
         <v>140</v>
@@ -16102,7 +16476,7 @@
         <v>1990</v>
       </c>
       <c r="E118" s="151" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F118" s="89" t="s">
         <v>140</v>
@@ -16119,7 +16493,7 @@
         <v>25000</v>
       </c>
       <c r="E119" s="151" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="120" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16133,7 +16507,7 @@
         <v>1600</v>
       </c>
       <c r="E120" s="151" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="121" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16147,7 +16521,7 @@
         <v>150</v>
       </c>
       <c r="E121" s="151" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="122" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16161,7 +16535,7 @@
         <v>2000</v>
       </c>
       <c r="E122" s="151" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="123" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16175,7 +16549,7 @@
         <v>3300</v>
       </c>
       <c r="E123" s="152" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="124" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16189,7 +16563,7 @@
         <v>25000</v>
       </c>
       <c r="E124" s="153" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="125" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16203,7 +16577,7 @@
         <v>25000</v>
       </c>
       <c r="E125" s="153" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="126" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16217,7 +16591,7 @@
         <v>640</v>
       </c>
       <c r="E126" s="153" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F126" s="89" t="s">
         <v>140</v>
@@ -16234,14 +16608,14 @@
         <v>400</v>
       </c>
       <c r="E127" s="153" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="128" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B128" s="347" t="s">
+      <c r="B128" s="350" t="s">
         <v>153</v>
       </c>
-      <c r="C128" s="348"/>
+      <c r="C128" s="351"/>
       <c r="D128" s="112">
         <f>SUM(D95:D127)</f>
         <v>291596</v>
@@ -16259,7 +16633,7 @@
         <v>2600</v>
       </c>
       <c r="E129" s="149" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F129" s="89"/>
     </row>
@@ -16274,7 +16648,7 @@
         <v>3643</v>
       </c>
       <c r="E130" s="65" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F130" s="89"/>
     </row>
@@ -16289,7 +16663,7 @@
         <v>600</v>
       </c>
       <c r="E131" s="171" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F131" s="89" t="s">
         <v>140</v>
@@ -16306,7 +16680,7 @@
         <v>500</v>
       </c>
       <c r="E132" s="145" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F132" s="89"/>
     </row>
@@ -16321,15 +16695,15 @@
         <v>260</v>
       </c>
       <c r="E133" s="145" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F133" s="89"/>
     </row>
     <row r="134" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B134" s="345" t="s">
+      <c r="B134" s="348" t="s">
         <v>153</v>
       </c>
-      <c r="C134" s="346"/>
+      <c r="C134" s="349"/>
       <c r="D134" s="115">
         <f>SUM(D129:D133)</f>
         <v>7603</v>
@@ -16347,7 +16721,7 @@
         <v>300</v>
       </c>
       <c r="E135" s="149" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F135" s="89"/>
     </row>
@@ -16362,7 +16736,7 @@
         <v>230</v>
       </c>
       <c r="E136" s="65" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F136" s="89"/>
     </row>
@@ -16377,7 +16751,7 @@
         <v>2100</v>
       </c>
       <c r="E137" s="171" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F137" s="89"/>
     </row>
@@ -16392,7 +16766,7 @@
         <v>8643</v>
       </c>
       <c r="E138" s="145" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F138" s="89" t="s">
         <v>140</v>
@@ -16409,7 +16783,7 @@
         <v>750</v>
       </c>
       <c r="E139" s="145" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F139" s="89"/>
     </row>
@@ -16424,15 +16798,15 @@
         <v>2100</v>
       </c>
       <c r="E140" s="149" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F140" s="89"/>
     </row>
     <row r="141" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B141" s="345" t="s">
+      <c r="B141" s="348" t="s">
         <v>153</v>
       </c>
-      <c r="C141" s="346"/>
+      <c r="C141" s="349"/>
       <c r="D141" s="115">
         <f>SUM(D135:D140)</f>
         <v>14123</v>
@@ -16450,7 +16824,7 @@
         <v>6124</v>
       </c>
       <c r="E142" s="65" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F142" s="89"/>
     </row>
@@ -16465,7 +16839,7 @@
         <v>1060</v>
       </c>
       <c r="E143" s="171" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F143" s="89"/>
     </row>
@@ -16480,15 +16854,15 @@
         <v>1730</v>
       </c>
       <c r="E144" s="171" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F144" s="89"/>
     </row>
     <row r="145" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B145" s="345" t="s">
+      <c r="B145" s="348" t="s">
         <v>153</v>
       </c>
-      <c r="C145" s="346"/>
+      <c r="C145" s="349"/>
       <c r="D145" s="115">
         <f>SUM(D142:D144)</f>
         <v>8914</v>
@@ -16506,7 +16880,7 @@
         <v>600</v>
       </c>
       <c r="E146" s="65" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F146" s="89"/>
     </row>
@@ -16521,7 +16895,7 @@
         <v>1200</v>
       </c>
       <c r="E147" s="65" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F147" s="89"/>
     </row>
@@ -16536,7 +16910,7 @@
         <v>10579</v>
       </c>
       <c r="E148" s="179" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F148" s="89"/>
     </row>
@@ -16551,7 +16925,7 @@
         <v>600</v>
       </c>
       <c r="E149" s="179" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F149" s="89"/>
     </row>
@@ -16566,7 +16940,7 @@
         <v>1500</v>
       </c>
       <c r="E150" s="179" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F150" s="89"/>
     </row>
@@ -16581,7 +16955,7 @@
         <v>1600</v>
       </c>
       <c r="E151" s="179" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F151" s="89"/>
     </row>
@@ -16596,15 +16970,15 @@
         <v>530</v>
       </c>
       <c r="E152" s="171" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F152" s="89"/>
     </row>
     <row r="153" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B153" s="345" t="s">
+      <c r="B153" s="348" t="s">
         <v>153</v>
       </c>
-      <c r="C153" s="346"/>
+      <c r="C153" s="349"/>
       <c r="D153" s="115">
         <f>SUM(D146:D152)</f>
         <v>16609</v>
@@ -16622,7 +16996,7 @@
         <v>7285</v>
       </c>
       <c r="E154" s="65" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F154" s="89"/>
     </row>
@@ -16637,7 +17011,7 @@
         <v>25000</v>
       </c>
       <c r="E155" s="65" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F155" s="89"/>
     </row>
@@ -16652,7 +17026,7 @@
         <v>10000</v>
       </c>
       <c r="E156" s="179" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F156" s="89"/>
     </row>
@@ -16667,7 +17041,7 @@
         <v>600</v>
       </c>
       <c r="E157" s="179" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F157" s="89"/>
     </row>
@@ -16682,7 +17056,7 @@
         <v>38000</v>
       </c>
       <c r="E158" s="194" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F158" s="89" t="s">
         <v>140</v>
@@ -16699,7 +17073,7 @@
         <v>100</v>
       </c>
       <c r="E159" s="179" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F159" s="89"/>
     </row>
@@ -16714,7 +17088,7 @@
         <v>205</v>
       </c>
       <c r="E160" s="179" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F160" s="89"/>
     </row>
@@ -16729,7 +17103,7 @@
         <v>300</v>
       </c>
       <c r="E161" s="179" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F161" s="89"/>
     </row>
@@ -16744,15 +17118,15 @@
         <v>1560</v>
       </c>
       <c r="E162" s="179" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F162" s="89"/>
     </row>
     <row r="163" spans="2:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B163" s="345" t="s">
+      <c r="B163" s="348" t="s">
         <v>153</v>
       </c>
-      <c r="C163" s="346"/>
+      <c r="C163" s="349"/>
       <c r="D163" s="115">
         <f>SUM(D154:D162)</f>
         <v>83050</v>
@@ -16770,7 +17144,7 @@
         <v>10057</v>
       </c>
       <c r="E164" s="195" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F164" s="89"/>
     </row>
@@ -16785,7 +17159,7 @@
         <v>600</v>
       </c>
       <c r="E165" s="195" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F165" s="89"/>
     </row>
@@ -16800,7 +17174,7 @@
         <v>195</v>
       </c>
       <c r="E166" s="196" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F166" s="89"/>
     </row>
@@ -16815,15 +17189,15 @@
         <v>200</v>
       </c>
       <c r="E167" s="196" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F167" s="89"/>
     </row>
     <row r="168" spans="2:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B168" s="345" t="s">
+      <c r="B168" s="348" t="s">
         <v>153</v>
       </c>
-      <c r="C168" s="346"/>
+      <c r="C168" s="349"/>
       <c r="D168" s="115">
         <f>SUM(D164:D167)</f>
         <v>11052</v>
@@ -16841,7 +17215,7 @@
         <v>8660</v>
       </c>
       <c r="E169" s="195" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F169" s="89"/>
     </row>
@@ -16856,7 +17230,7 @@
         <v>200</v>
       </c>
       <c r="E170" s="195" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F170" s="89"/>
     </row>
@@ -16879,10 +17253,10 @@
       <c r="F172" s="89"/>
     </row>
     <row r="173" spans="2:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B173" s="345" t="s">
+      <c r="B173" s="348" t="s">
         <v>153</v>
       </c>
-      <c r="C173" s="346"/>
+      <c r="C173" s="349"/>
       <c r="D173" s="115">
         <f>SUM(D169:D172)</f>
         <v>8860</v>
@@ -16890,1604 +17264,1704 @@
       <c r="E173" s="45"/>
     </row>
     <row r="174" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B174" s="259">
+      <c r="B174" s="258">
         <v>1</v>
       </c>
-      <c r="C174" s="260">
+      <c r="C174" s="259">
         <v>45874</v>
       </c>
-      <c r="D174" s="261">
+      <c r="D174" s="260">
         <v>10273</v>
       </c>
-      <c r="E174" s="262" t="s">
+      <c r="E174" s="261" t="s">
+        <v>329</v>
+      </c>
+      <c r="F174" s="262"/>
+      <c r="G174" s="343"/>
+      <c r="H174" s="343"/>
+      <c r="I174" s="343"/>
+      <c r="J174" s="343"/>
+      <c r="K174" s="343"/>
+      <c r="L174" s="343"/>
+      <c r="M174" s="343"/>
+      <c r="N174" s="343"/>
+    </row>
+    <row r="175" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B175" s="258">
+        <v>2</v>
+      </c>
+      <c r="C175" s="259">
+        <v>45877</v>
+      </c>
+      <c r="D175" s="260">
+        <v>100</v>
+      </c>
+      <c r="E175" s="261" t="s">
         <v>330</v>
       </c>
-      <c r="F174" s="263"/>
-      <c r="G174" s="340"/>
-      <c r="H174" s="340"/>
-      <c r="I174" s="340"/>
-      <c r="J174" s="340"/>
-      <c r="K174" s="340"/>
-      <c r="L174" s="340"/>
-      <c r="M174" s="340"/>
-      <c r="N174" s="340"/>
-    </row>
-    <row r="175" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B175" s="259">
+      <c r="F175" s="262"/>
+      <c r="G175" s="255"/>
+      <c r="H175" s="255"/>
+      <c r="I175" s="255"/>
+      <c r="J175" s="255"/>
+      <c r="K175" s="255"/>
+      <c r="L175" s="255"/>
+      <c r="M175" s="255"/>
+      <c r="N175" s="255"/>
+    </row>
+    <row r="176" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B176" s="258">
+        <v>3</v>
+      </c>
+      <c r="C176" s="259">
+        <v>45878</v>
+      </c>
+      <c r="D176" s="260">
+        <v>600</v>
+      </c>
+      <c r="E176" s="261" t="s">
+        <v>331</v>
+      </c>
+      <c r="F176" s="262"/>
+      <c r="G176" s="255"/>
+      <c r="H176" s="255"/>
+      <c r="I176" s="255"/>
+      <c r="J176" s="255"/>
+      <c r="K176" s="255"/>
+      <c r="L176" s="255"/>
+      <c r="M176" s="255"/>
+      <c r="N176" s="255"/>
+    </row>
+    <row r="177" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B177" s="258">
+        <v>4</v>
+      </c>
+      <c r="C177" s="259">
+        <v>45876</v>
+      </c>
+      <c r="D177" s="260">
+        <v>500</v>
+      </c>
+      <c r="E177" s="261" t="s">
+        <v>332</v>
+      </c>
+      <c r="F177" s="262"/>
+      <c r="G177" s="255"/>
+      <c r="H177" s="255"/>
+      <c r="I177" s="255"/>
+      <c r="J177" s="255"/>
+      <c r="K177" s="255"/>
+      <c r="L177" s="255"/>
+      <c r="M177" s="255"/>
+      <c r="N177" s="255"/>
+    </row>
+    <row r="178" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B178" s="258">
+        <v>5</v>
+      </c>
+      <c r="C178" s="259">
+        <v>45881</v>
+      </c>
+      <c r="D178" s="260">
+        <v>895</v>
+      </c>
+      <c r="E178" s="261" t="s">
+        <v>333</v>
+      </c>
+      <c r="F178" s="262"/>
+      <c r="G178" s="255"/>
+      <c r="H178" s="255"/>
+      <c r="I178" s="255"/>
+      <c r="J178" s="255"/>
+      <c r="K178" s="255"/>
+      <c r="L178" s="255"/>
+      <c r="M178" s="255"/>
+      <c r="N178" s="255"/>
+    </row>
+    <row r="179" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B179" s="263" t="s">
+        <v>153</v>
+      </c>
+      <c r="C179" s="273"/>
+      <c r="D179" s="264">
+        <v>12368</v>
+      </c>
+      <c r="E179" s="265"/>
+      <c r="F179" s="274"/>
+      <c r="G179" s="255"/>
+      <c r="H179" s="255"/>
+      <c r="I179" s="255"/>
+      <c r="J179" s="255"/>
+      <c r="K179" s="255"/>
+      <c r="L179" s="255"/>
+      <c r="M179" s="255"/>
+      <c r="N179" s="255"/>
+    </row>
+    <row r="180" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B180" s="258">
+        <v>1</v>
+      </c>
+      <c r="C180" s="259">
+        <v>45902</v>
+      </c>
+      <c r="D180" s="260">
+        <v>600</v>
+      </c>
+      <c r="E180" s="261" t="s">
+        <v>334</v>
+      </c>
+      <c r="F180" s="262"/>
+      <c r="G180" s="255"/>
+      <c r="H180" s="255"/>
+      <c r="I180" s="255"/>
+      <c r="J180" s="255"/>
+      <c r="K180" s="255"/>
+      <c r="L180" s="255"/>
+      <c r="M180" s="255"/>
+      <c r="N180" s="255"/>
+    </row>
+    <row r="181" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B181" s="258">
         <v>2</v>
       </c>
-      <c r="C175" s="260">
-        <v>45877</v>
-      </c>
-      <c r="D175" s="261">
-        <v>100</v>
-      </c>
-      <c r="E175" s="262" t="s">
-        <v>331</v>
-      </c>
-      <c r="F175" s="263"/>
-      <c r="G175" s="256"/>
-      <c r="H175" s="256"/>
-      <c r="I175" s="256"/>
-      <c r="J175" s="256"/>
-      <c r="K175" s="256"/>
-      <c r="L175" s="256"/>
-      <c r="M175" s="256"/>
-      <c r="N175" s="256"/>
-    </row>
-    <row r="176" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B176" s="259">
+      <c r="C181" s="259">
+        <v>45884</v>
+      </c>
+      <c r="D181" s="260">
+        <v>420</v>
+      </c>
+      <c r="E181" s="261" t="s">
+        <v>335</v>
+      </c>
+      <c r="F181" s="262"/>
+      <c r="G181" s="255"/>
+      <c r="H181" s="255"/>
+      <c r="I181" s="255"/>
+      <c r="J181" s="255"/>
+      <c r="K181" s="255"/>
+      <c r="L181" s="255"/>
+      <c r="M181" s="255"/>
+      <c r="N181" s="255"/>
+    </row>
+    <row r="182" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B182" s="258">
         <v>3</v>
       </c>
-      <c r="C176" s="260">
-        <v>45878</v>
-      </c>
-      <c r="D176" s="261">
-        <v>600</v>
-      </c>
-      <c r="E176" s="262" t="s">
-        <v>332</v>
-      </c>
-      <c r="F176" s="263"/>
-      <c r="G176" s="256"/>
-      <c r="H176" s="256"/>
-      <c r="I176" s="256"/>
-      <c r="J176" s="256"/>
-      <c r="K176" s="256"/>
-      <c r="L176" s="256"/>
-      <c r="M176" s="256"/>
-      <c r="N176" s="256"/>
-    </row>
-    <row r="177" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B177" s="259">
+      <c r="C182" s="259">
+        <v>45905</v>
+      </c>
+      <c r="D182" s="260">
+        <v>9934</v>
+      </c>
+      <c r="E182" s="261" t="s">
+        <v>281</v>
+      </c>
+      <c r="F182" s="262"/>
+      <c r="G182" s="255"/>
+      <c r="H182" s="255"/>
+      <c r="I182" s="255"/>
+      <c r="J182" s="255"/>
+      <c r="K182" s="255"/>
+      <c r="L182" s="255"/>
+      <c r="M182" s="255"/>
+      <c r="N182" s="255"/>
+    </row>
+    <row r="183" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B183" s="258">
         <v>4</v>
       </c>
-      <c r="C177" s="260">
-        <v>45876</v>
-      </c>
-      <c r="D177" s="261">
-        <v>500</v>
-      </c>
-      <c r="E177" s="262" t="s">
-        <v>333</v>
-      </c>
-      <c r="F177" s="263"/>
-      <c r="G177" s="256"/>
-      <c r="H177" s="256"/>
-      <c r="I177" s="256"/>
-      <c r="J177" s="256"/>
-      <c r="K177" s="256"/>
-      <c r="L177" s="256"/>
-      <c r="M177" s="256"/>
-      <c r="N177" s="256"/>
-    </row>
-    <row r="178" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B178" s="259">
+      <c r="C183" s="259">
+        <v>45908</v>
+      </c>
+      <c r="D183" s="260">
+        <v>1700</v>
+      </c>
+      <c r="E183" s="261" t="s">
+        <v>336</v>
+      </c>
+      <c r="F183" s="275" t="s">
+        <v>140</v>
+      </c>
+      <c r="G183" s="89"/>
+      <c r="H183" s="255"/>
+      <c r="I183" s="255"/>
+      <c r="J183" s="255"/>
+      <c r="K183" s="255"/>
+      <c r="L183" s="255"/>
+      <c r="M183" s="255"/>
+      <c r="N183" s="255"/>
+    </row>
+    <row r="184" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B184" s="258">
         <v>5</v>
       </c>
-      <c r="C178" s="260">
-        <v>45881</v>
-      </c>
-      <c r="D178" s="261">
-        <v>895</v>
-      </c>
-      <c r="E178" s="262" t="s">
-        <v>334</v>
-      </c>
-      <c r="F178" s="263"/>
-      <c r="G178" s="256"/>
-      <c r="H178" s="256"/>
-      <c r="I178" s="256"/>
-      <c r="J178" s="256"/>
-      <c r="K178" s="256"/>
-      <c r="L178" s="256"/>
-      <c r="M178" s="256"/>
-      <c r="N178" s="256"/>
-    </row>
-    <row r="179" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B179" s="264" t="s">
+      <c r="C184" s="259">
+        <v>45909</v>
+      </c>
+      <c r="D184" s="260">
+        <v>340</v>
+      </c>
+      <c r="E184" s="261" t="s">
+        <v>337</v>
+      </c>
+      <c r="F184" s="262"/>
+      <c r="G184" s="255"/>
+      <c r="H184" s="255"/>
+      <c r="I184" s="255"/>
+      <c r="J184" s="255"/>
+      <c r="K184" s="255"/>
+      <c r="L184" s="255"/>
+      <c r="M184" s="255"/>
+      <c r="N184" s="255"/>
+    </row>
+    <row r="185" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B185" s="263" t="s">
         <v>153</v>
       </c>
-      <c r="C179" s="274"/>
-      <c r="D179" s="265">
-        <v>12368</v>
-      </c>
-      <c r="E179" s="266"/>
-      <c r="F179" s="275"/>
-      <c r="G179" s="256"/>
-      <c r="H179" s="256"/>
-      <c r="I179" s="256"/>
-      <c r="J179" s="256"/>
-      <c r="K179" s="256"/>
-      <c r="L179" s="256"/>
-      <c r="M179" s="256"/>
-      <c r="N179" s="256"/>
-    </row>
-    <row r="180" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B180" s="259">
+      <c r="C185" s="273"/>
+      <c r="D185" s="264">
+        <v>12994</v>
+      </c>
+      <c r="E185" s="265"/>
+      <c r="F185" s="274"/>
+      <c r="G185" s="255"/>
+      <c r="H185" s="255"/>
+      <c r="I185" s="255"/>
+      <c r="J185" s="255"/>
+      <c r="K185" s="255"/>
+      <c r="L185" s="255"/>
+      <c r="M185" s="255"/>
+      <c r="N185" s="255"/>
+    </row>
+    <row r="186" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B186" s="258">
         <v>1</v>
       </c>
-      <c r="C180" s="260">
-        <v>45902</v>
-      </c>
-      <c r="D180" s="261">
-        <v>600</v>
-      </c>
-      <c r="E180" s="262" t="s">
-        <v>335</v>
-      </c>
-      <c r="F180" s="263"/>
-      <c r="G180" s="256"/>
-      <c r="H180" s="256"/>
-      <c r="I180" s="256"/>
-      <c r="J180" s="256"/>
-      <c r="K180" s="256"/>
-      <c r="L180" s="256"/>
-      <c r="M180" s="256"/>
-      <c r="N180" s="256"/>
-    </row>
-    <row r="181" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B181" s="259">
+      <c r="C186" s="259">
+        <v>45934</v>
+      </c>
+      <c r="D186" s="260">
+        <v>8787</v>
+      </c>
+      <c r="E186" s="261" t="s">
+        <v>281</v>
+      </c>
+      <c r="F186" s="262"/>
+      <c r="G186" s="255"/>
+      <c r="H186" s="255"/>
+      <c r="I186" s="255"/>
+      <c r="J186" s="255"/>
+      <c r="K186" s="255"/>
+      <c r="L186" s="255"/>
+      <c r="M186" s="255"/>
+      <c r="N186" s="255"/>
+    </row>
+    <row r="187" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B187" s="258">
         <v>2</v>
       </c>
-      <c r="C181" s="260">
-        <v>45884</v>
-      </c>
-      <c r="D181" s="261">
-        <v>420</v>
-      </c>
-      <c r="E181" s="262" t="s">
-        <v>336</v>
-      </c>
-      <c r="F181" s="263"/>
-      <c r="G181" s="256"/>
-      <c r="H181" s="256"/>
-      <c r="I181" s="256"/>
-      <c r="J181" s="256"/>
-      <c r="K181" s="256"/>
-      <c r="L181" s="256"/>
-      <c r="M181" s="256"/>
-      <c r="N181" s="256"/>
-    </row>
-    <row r="182" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B182" s="259">
+      <c r="C187" s="259">
+        <v>45938</v>
+      </c>
+      <c r="D187" s="260">
+        <v>390</v>
+      </c>
+      <c r="E187" s="261" t="s">
+        <v>338</v>
+      </c>
+      <c r="F187" s="262"/>
+      <c r="G187" s="255"/>
+      <c r="H187" s="255"/>
+      <c r="I187" s="255"/>
+      <c r="J187" s="255"/>
+      <c r="K187" s="255"/>
+      <c r="L187" s="255"/>
+      <c r="M187" s="255"/>
+      <c r="N187" s="255"/>
+    </row>
+    <row r="188" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B188" s="258">
         <v>3</v>
       </c>
-      <c r="C182" s="260">
-        <v>45905</v>
-      </c>
-      <c r="D182" s="261">
-        <v>9934</v>
-      </c>
-      <c r="E182" s="262" t="s">
-        <v>282</v>
-      </c>
-      <c r="F182" s="263"/>
-      <c r="G182" s="256"/>
-      <c r="H182" s="256"/>
-      <c r="I182" s="256"/>
-      <c r="J182" s="256"/>
-      <c r="K182" s="256"/>
-      <c r="L182" s="256"/>
-      <c r="M182" s="256"/>
-      <c r="N182" s="256"/>
-    </row>
-    <row r="183" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B183" s="259">
+      <c r="C188" s="259">
+        <v>45941</v>
+      </c>
+      <c r="D188" s="266">
+        <v>500</v>
+      </c>
+      <c r="E188" s="261" t="s">
+        <v>339</v>
+      </c>
+      <c r="F188" s="262"/>
+      <c r="G188" s="255"/>
+      <c r="H188" s="255"/>
+      <c r="I188" s="255"/>
+      <c r="J188" s="255"/>
+      <c r="K188" s="255"/>
+      <c r="L188" s="255"/>
+      <c r="M188" s="255"/>
+      <c r="N188" s="255"/>
+    </row>
+    <row r="189" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B189" s="258">
         <v>4</v>
       </c>
-      <c r="C183" s="260">
-        <v>45908</v>
-      </c>
-      <c r="D183" s="261">
-        <v>1700</v>
-      </c>
-      <c r="E183" s="262" t="s">
-        <v>337</v>
-      </c>
-      <c r="F183" s="276" t="s">
+      <c r="C189" s="259">
+        <v>45941</v>
+      </c>
+      <c r="D189" s="266">
+        <v>9500</v>
+      </c>
+      <c r="E189" s="261" t="s">
+        <v>340</v>
+      </c>
+      <c r="F189" s="262"/>
+      <c r="G189" s="255"/>
+      <c r="H189" s="255"/>
+      <c r="I189" s="255"/>
+      <c r="J189" s="255"/>
+      <c r="K189" s="255"/>
+      <c r="L189" s="255"/>
+      <c r="M189" s="255"/>
+      <c r="N189" s="255"/>
+    </row>
+    <row r="190" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B190" s="258">
+        <v>5</v>
+      </c>
+      <c r="C190" s="259">
+        <v>45942</v>
+      </c>
+      <c r="D190" s="266">
+        <v>5000</v>
+      </c>
+      <c r="E190" s="261" t="s">
+        <v>341</v>
+      </c>
+      <c r="F190" s="262"/>
+      <c r="G190" s="255"/>
+      <c r="H190" s="255"/>
+      <c r="I190" s="255"/>
+      <c r="J190" s="255"/>
+      <c r="K190" s="255"/>
+      <c r="L190" s="255"/>
+      <c r="M190" s="255"/>
+      <c r="N190" s="255"/>
+    </row>
+    <row r="191" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B191" s="258">
+        <v>6</v>
+      </c>
+      <c r="C191" s="259">
+        <v>45942</v>
+      </c>
+      <c r="D191" s="266">
+        <v>1500</v>
+      </c>
+      <c r="E191" s="261" t="s">
+        <v>342</v>
+      </c>
+      <c r="F191" s="262"/>
+      <c r="G191" s="255"/>
+      <c r="H191" s="255"/>
+      <c r="I191" s="255"/>
+      <c r="J191" s="255"/>
+      <c r="K191" s="255"/>
+      <c r="L191" s="255"/>
+      <c r="M191" s="255"/>
+      <c r="N191" s="255"/>
+    </row>
+    <row r="192" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B192" s="258">
+        <v>7</v>
+      </c>
+      <c r="C192" s="259">
+        <v>45943</v>
+      </c>
+      <c r="D192" s="266">
+        <v>2000</v>
+      </c>
+      <c r="E192" s="261" t="s">
+        <v>343</v>
+      </c>
+      <c r="F192" s="262"/>
+      <c r="G192" s="255"/>
+      <c r="H192" s="255"/>
+      <c r="I192" s="255"/>
+      <c r="J192" s="255"/>
+      <c r="K192" s="255"/>
+      <c r="L192" s="255"/>
+      <c r="M192" s="255"/>
+      <c r="N192" s="255"/>
+    </row>
+    <row r="193" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B193" s="258">
+        <v>8</v>
+      </c>
+      <c r="C193" s="259">
+        <v>45943</v>
+      </c>
+      <c r="D193" s="266">
+        <v>2500</v>
+      </c>
+      <c r="E193" s="261" t="s">
+        <v>342</v>
+      </c>
+      <c r="F193" s="262"/>
+      <c r="G193" s="255"/>
+      <c r="H193" s="255"/>
+      <c r="I193" s="255"/>
+      <c r="J193" s="255"/>
+      <c r="K193" s="255"/>
+      <c r="L193" s="255"/>
+      <c r="M193" s="255"/>
+      <c r="N193" s="255"/>
+    </row>
+    <row r="194" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B194" s="258">
+        <v>9</v>
+      </c>
+      <c r="C194" s="259">
+        <v>45944</v>
+      </c>
+      <c r="D194" s="266">
+        <v>2000</v>
+      </c>
+      <c r="E194" s="261" t="s">
+        <v>342</v>
+      </c>
+      <c r="F194" s="262"/>
+      <c r="G194" s="255"/>
+      <c r="H194" s="255"/>
+      <c r="I194" s="255"/>
+      <c r="J194" s="255"/>
+      <c r="K194" s="255"/>
+      <c r="L194" s="255"/>
+      <c r="M194" s="255"/>
+      <c r="N194" s="255"/>
+    </row>
+    <row r="195" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B195" s="258">
+        <v>10</v>
+      </c>
+      <c r="C195" s="259">
+        <v>45944</v>
+      </c>
+      <c r="D195" s="266">
+        <v>317</v>
+      </c>
+      <c r="E195" s="261" t="s">
+        <v>344</v>
+      </c>
+      <c r="F195" s="275" t="s">
         <v>140</v>
       </c>
-      <c r="G183" s="89"/>
-      <c r="H183" s="256"/>
-      <c r="I183" s="256"/>
-      <c r="J183" s="256"/>
-      <c r="K183" s="256"/>
-      <c r="L183" s="256"/>
-      <c r="M183" s="256"/>
-      <c r="N183" s="256"/>
-    </row>
-    <row r="184" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B184" s="259">
+      <c r="G195" s="89"/>
+      <c r="H195" s="255"/>
+      <c r="I195" s="255"/>
+      <c r="J195" s="255"/>
+      <c r="K195" s="255"/>
+      <c r="L195" s="255"/>
+      <c r="M195" s="255"/>
+      <c r="N195" s="255"/>
+    </row>
+    <row r="196" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B196" s="258">
+        <v>11</v>
+      </c>
+      <c r="C196" s="259">
+        <v>45944</v>
+      </c>
+      <c r="D196" s="266">
+        <v>800</v>
+      </c>
+      <c r="E196" s="261" t="s">
+        <v>345</v>
+      </c>
+      <c r="F196" s="262"/>
+      <c r="G196" s="255"/>
+      <c r="H196" s="255"/>
+      <c r="I196" s="255"/>
+      <c r="J196" s="255"/>
+      <c r="K196" s="255"/>
+      <c r="L196" s="255"/>
+      <c r="M196" s="255"/>
+      <c r="N196" s="255"/>
+    </row>
+    <row r="197" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B197" s="258">
+        <v>12</v>
+      </c>
+      <c r="C197" s="259">
+        <v>45945</v>
+      </c>
+      <c r="D197" s="266">
+        <v>800</v>
+      </c>
+      <c r="E197" s="261" t="s">
+        <v>346</v>
+      </c>
+      <c r="F197" s="262"/>
+      <c r="G197" s="255"/>
+      <c r="H197" s="255"/>
+      <c r="I197" s="255"/>
+      <c r="J197" s="255"/>
+      <c r="K197" s="255"/>
+      <c r="L197" s="255"/>
+      <c r="M197" s="255"/>
+      <c r="N197" s="255"/>
+    </row>
+    <row r="198" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B198" s="258">
+        <v>13</v>
+      </c>
+      <c r="C198" s="259">
+        <v>45945</v>
+      </c>
+      <c r="D198" s="266">
+        <v>800</v>
+      </c>
+      <c r="E198" s="261" t="s">
+        <v>347</v>
+      </c>
+      <c r="F198" s="262"/>
+      <c r="G198" s="255"/>
+      <c r="H198" s="255"/>
+      <c r="I198" s="255"/>
+      <c r="J198" s="255"/>
+      <c r="K198" s="255"/>
+      <c r="L198" s="255"/>
+      <c r="M198" s="255"/>
+      <c r="N198" s="255"/>
+    </row>
+    <row r="199" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B199" s="258">
+        <v>14</v>
+      </c>
+      <c r="C199" s="259">
+        <v>45945</v>
+      </c>
+      <c r="D199" s="266">
+        <v>500</v>
+      </c>
+      <c r="E199" s="261" t="s">
+        <v>342</v>
+      </c>
+      <c r="F199" s="262"/>
+      <c r="G199" s="255"/>
+      <c r="H199" s="255"/>
+      <c r="I199" s="255"/>
+      <c r="J199" s="255"/>
+      <c r="K199" s="255"/>
+      <c r="L199" s="255"/>
+      <c r="M199" s="255"/>
+      <c r="N199" s="255"/>
+    </row>
+    <row r="200" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B200" s="258">
+        <v>15</v>
+      </c>
+      <c r="C200" s="259">
+        <v>45946</v>
+      </c>
+      <c r="D200" s="266">
+        <v>1500</v>
+      </c>
+      <c r="E200" s="261" t="s">
+        <v>348</v>
+      </c>
+      <c r="F200" s="262"/>
+      <c r="G200" s="255"/>
+      <c r="H200" s="255"/>
+      <c r="I200" s="255"/>
+      <c r="J200" s="255"/>
+      <c r="K200" s="255"/>
+      <c r="L200" s="255"/>
+      <c r="M200" s="255"/>
+      <c r="N200" s="255"/>
+    </row>
+    <row r="201" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B201" s="258">
+        <v>16</v>
+      </c>
+      <c r="C201" s="259">
+        <v>45947</v>
+      </c>
+      <c r="D201" s="266">
+        <v>15000</v>
+      </c>
+      <c r="E201" s="267" t="s">
+        <v>349</v>
+      </c>
+      <c r="F201" s="275" t="s">
+        <v>140</v>
+      </c>
+      <c r="G201" s="89"/>
+      <c r="H201" s="255"/>
+      <c r="I201" s="255"/>
+      <c r="J201" s="255"/>
+      <c r="K201" s="255"/>
+      <c r="L201" s="255"/>
+      <c r="M201" s="255"/>
+      <c r="N201" s="255"/>
+    </row>
+    <row r="202" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B202" s="258">
+        <v>13</v>
+      </c>
+      <c r="C202" s="259">
+        <v>45948</v>
+      </c>
+      <c r="D202" s="266">
+        <v>5700</v>
+      </c>
+      <c r="E202" s="261" t="s">
+        <v>350</v>
+      </c>
+      <c r="F202" s="262"/>
+      <c r="G202" s="255"/>
+      <c r="H202" s="255"/>
+      <c r="I202" s="255"/>
+      <c r="J202" s="255"/>
+      <c r="K202" s="255"/>
+      <c r="L202" s="255"/>
+      <c r="M202" s="255"/>
+      <c r="N202" s="255"/>
+    </row>
+    <row r="203" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B203" s="258">
+        <v>14</v>
+      </c>
+      <c r="C203" s="259">
+        <v>45953</v>
+      </c>
+      <c r="D203" s="266">
+        <v>500</v>
+      </c>
+      <c r="E203" s="261" t="s">
+        <v>351</v>
+      </c>
+      <c r="F203" s="262"/>
+      <c r="G203" s="255"/>
+      <c r="H203" s="255"/>
+      <c r="I203" s="255"/>
+      <c r="J203" s="255"/>
+      <c r="K203" s="255"/>
+      <c r="L203" s="255"/>
+      <c r="M203" s="255"/>
+      <c r="N203" s="255"/>
+    </row>
+    <row r="204" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B204" s="258">
+        <v>15</v>
+      </c>
+      <c r="C204" s="260"/>
+      <c r="D204" s="268"/>
+      <c r="E204" s="261"/>
+      <c r="F204" s="262"/>
+      <c r="G204" s="255"/>
+      <c r="H204" s="255"/>
+      <c r="I204" s="255"/>
+      <c r="J204" s="255"/>
+      <c r="K204" s="255"/>
+      <c r="L204" s="255"/>
+      <c r="M204" s="255"/>
+      <c r="N204" s="255"/>
+    </row>
+    <row r="205" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B205" s="263" t="s">
+        <v>153</v>
+      </c>
+      <c r="C205" s="273"/>
+      <c r="D205" s="264">
+        <v>58094</v>
+      </c>
+      <c r="E205" s="265"/>
+      <c r="F205" s="274"/>
+      <c r="G205" s="255"/>
+      <c r="H205" s="255"/>
+      <c r="I205" s="255"/>
+      <c r="J205" s="255"/>
+      <c r="K205" s="255"/>
+      <c r="L205" s="255"/>
+      <c r="M205" s="255"/>
+      <c r="N205" s="255"/>
+    </row>
+    <row r="206" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B206" s="258">
+        <v>1</v>
+      </c>
+      <c r="C206" s="259">
+        <v>45966</v>
+      </c>
+      <c r="D206" s="266">
+        <v>11964</v>
+      </c>
+      <c r="E206" s="261" t="s">
+        <v>352</v>
+      </c>
+      <c r="F206" s="262"/>
+      <c r="G206" s="255"/>
+      <c r="H206" s="255"/>
+      <c r="I206" s="255"/>
+      <c r="J206" s="255"/>
+      <c r="K206" s="255"/>
+      <c r="L206" s="255"/>
+      <c r="M206" s="255"/>
+      <c r="N206" s="255"/>
+    </row>
+    <row r="207" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B207" s="258">
+        <v>2</v>
+      </c>
+      <c r="C207" s="259">
+        <v>45967</v>
+      </c>
+      <c r="D207" s="266">
+        <v>500</v>
+      </c>
+      <c r="E207" s="261" t="s">
+        <v>353</v>
+      </c>
+      <c r="F207" s="262"/>
+      <c r="G207" s="255"/>
+      <c r="H207" s="255"/>
+      <c r="I207" s="255"/>
+      <c r="J207" s="255"/>
+      <c r="K207" s="255"/>
+      <c r="L207" s="255"/>
+      <c r="M207" s="255"/>
+      <c r="N207" s="255"/>
+    </row>
+    <row r="208" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B208" s="258">
+        <v>3</v>
+      </c>
+      <c r="C208" s="259">
+        <v>45969</v>
+      </c>
+      <c r="D208" s="260">
+        <v>600</v>
+      </c>
+      <c r="E208" s="261" t="s">
+        <v>354</v>
+      </c>
+      <c r="F208" s="262"/>
+      <c r="G208" s="255"/>
+      <c r="H208" s="255"/>
+      <c r="I208" s="255"/>
+      <c r="J208" s="255"/>
+      <c r="K208" s="255"/>
+      <c r="L208" s="255"/>
+      <c r="M208" s="255"/>
+      <c r="N208" s="255"/>
+    </row>
+    <row r="209" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B209" s="263" t="s">
+        <v>153</v>
+      </c>
+      <c r="C209" s="273"/>
+      <c r="D209" s="264">
+        <v>13064</v>
+      </c>
+      <c r="E209" s="265"/>
+      <c r="F209" s="274"/>
+      <c r="G209" s="255"/>
+      <c r="H209" s="255"/>
+      <c r="I209" s="255"/>
+      <c r="J209" s="255"/>
+      <c r="K209" s="255"/>
+      <c r="L209" s="255"/>
+      <c r="M209" s="255"/>
+      <c r="N209" s="255"/>
+    </row>
+    <row r="210" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B210" s="258">
+        <v>1</v>
+      </c>
+      <c r="C210" s="259">
+        <v>45993</v>
+      </c>
+      <c r="D210" s="266">
+        <v>8784</v>
+      </c>
+      <c r="E210" s="261" t="s">
+        <v>355</v>
+      </c>
+      <c r="F210" s="262"/>
+      <c r="G210" s="255"/>
+      <c r="H210" s="255"/>
+      <c r="I210" s="255"/>
+      <c r="J210" s="255"/>
+      <c r="K210" s="255"/>
+      <c r="L210" s="255"/>
+      <c r="M210" s="255"/>
+      <c r="N210" s="255"/>
+    </row>
+    <row r="211" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B211" s="258">
+        <v>2</v>
+      </c>
+      <c r="C211" s="259">
+        <v>46011</v>
+      </c>
+      <c r="D211" s="266">
+        <v>1570</v>
+      </c>
+      <c r="E211" s="261" t="s">
+        <v>356</v>
+      </c>
+      <c r="F211" s="262"/>
+      <c r="G211" s="255"/>
+      <c r="H211" s="255"/>
+      <c r="I211" s="255"/>
+      <c r="J211" s="255"/>
+      <c r="K211" s="255"/>
+      <c r="L211" s="255"/>
+      <c r="M211" s="255"/>
+      <c r="N211" s="255"/>
+    </row>
+    <row r="212" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B212" s="258">
+        <v>3</v>
+      </c>
+      <c r="C212" s="259">
+        <v>46014</v>
+      </c>
+      <c r="D212" s="260">
+        <v>4000</v>
+      </c>
+      <c r="E212" s="269" t="s">
+        <v>357</v>
+      </c>
+      <c r="F212" s="262"/>
+      <c r="G212" s="255"/>
+      <c r="H212" s="255"/>
+      <c r="I212" s="255"/>
+      <c r="J212" s="255"/>
+      <c r="K212" s="255"/>
+      <c r="L212" s="255"/>
+      <c r="M212" s="255"/>
+      <c r="N212" s="255"/>
+    </row>
+    <row r="213" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B213" s="263" t="s">
+        <v>153</v>
+      </c>
+      <c r="C213" s="273"/>
+      <c r="D213" s="264">
+        <v>14354</v>
+      </c>
+      <c r="E213" s="265"/>
+      <c r="F213" s="274"/>
+      <c r="G213" s="255"/>
+      <c r="H213" s="255"/>
+      <c r="I213" s="255"/>
+      <c r="J213" s="255"/>
+      <c r="K213" s="255"/>
+      <c r="L213" s="255"/>
+      <c r="M213" s="255"/>
+      <c r="N213" s="255"/>
+    </row>
+    <row r="214" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B214" s="258">
+        <v>1</v>
+      </c>
+      <c r="C214" s="259">
+        <v>46023</v>
+      </c>
+      <c r="D214" s="266">
+        <v>9449</v>
+      </c>
+      <c r="E214" s="261" t="s">
+        <v>358</v>
+      </c>
+      <c r="F214" s="262"/>
+      <c r="G214" s="255"/>
+      <c r="H214" s="255"/>
+      <c r="I214" s="255"/>
+      <c r="J214" s="255"/>
+      <c r="K214" s="255"/>
+      <c r="L214" s="255"/>
+      <c r="M214" s="255"/>
+      <c r="N214" s="255"/>
+    </row>
+    <row r="215" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B215" s="263" t="s">
+        <v>153</v>
+      </c>
+      <c r="C215" s="273"/>
+      <c r="D215" s="264">
+        <v>9449</v>
+      </c>
+      <c r="E215" s="265"/>
+      <c r="F215" s="274"/>
+      <c r="G215" s="255"/>
+      <c r="H215" s="255"/>
+      <c r="I215" s="255"/>
+      <c r="J215" s="255"/>
+      <c r="K215" s="255"/>
+      <c r="L215" s="255"/>
+      <c r="M215" s="255"/>
+      <c r="N215" s="255"/>
+    </row>
+    <row r="216" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B216" s="258">
+        <v>1</v>
+      </c>
+      <c r="C216" s="259">
+        <v>46057</v>
+      </c>
+      <c r="D216" s="266">
+        <v>825</v>
+      </c>
+      <c r="E216" s="261" t="s">
+        <v>359</v>
+      </c>
+      <c r="F216" s="262"/>
+      <c r="G216" s="255"/>
+      <c r="H216" s="255"/>
+      <c r="I216" s="255"/>
+      <c r="J216" s="255"/>
+      <c r="K216" s="255"/>
+      <c r="L216" s="255"/>
+      <c r="M216" s="255"/>
+      <c r="N216" s="255"/>
+    </row>
+    <row r="217" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B217" s="258">
+        <v>2</v>
+      </c>
+      <c r="C217" s="259">
+        <v>46057</v>
+      </c>
+      <c r="D217" s="266">
+        <v>9172</v>
+      </c>
+      <c r="E217" s="261" t="s">
+        <v>360</v>
+      </c>
+      <c r="F217" s="262"/>
+      <c r="G217" s="255"/>
+      <c r="H217" s="255"/>
+      <c r="I217" s="255"/>
+      <c r="J217" s="255"/>
+      <c r="K217" s="255"/>
+      <c r="L217" s="255"/>
+      <c r="M217" s="255"/>
+      <c r="N217" s="255"/>
+    </row>
+    <row r="218" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B218" s="263" t="s">
+        <v>153</v>
+      </c>
+      <c r="C218" s="273"/>
+      <c r="D218" s="264">
+        <v>9997</v>
+      </c>
+      <c r="E218" s="265"/>
+      <c r="F218" s="274"/>
+      <c r="G218" s="255"/>
+      <c r="H218" s="255"/>
+      <c r="I218" s="255"/>
+      <c r="J218" s="255"/>
+      <c r="K218" s="255"/>
+      <c r="L218" s="255"/>
+      <c r="M218" s="255"/>
+      <c r="N218" s="255"/>
+    </row>
+    <row r="219" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B219" s="258">
+        <v>1</v>
+      </c>
+      <c r="C219" s="259">
+        <v>46083</v>
+      </c>
+      <c r="D219" s="266">
+        <v>11500</v>
+      </c>
+      <c r="E219" s="261" t="s">
+        <v>361</v>
+      </c>
+      <c r="F219" s="262"/>
+      <c r="G219" s="255"/>
+      <c r="H219" s="255"/>
+      <c r="I219" s="255"/>
+      <c r="J219" s="255"/>
+      <c r="K219" s="255"/>
+      <c r="L219" s="255"/>
+      <c r="M219" s="255"/>
+      <c r="N219" s="255"/>
+    </row>
+    <row r="220" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B220" s="258">
+        <v>2</v>
+      </c>
+      <c r="C220" s="259">
+        <v>46083</v>
+      </c>
+      <c r="D220" s="266">
+        <v>535</v>
+      </c>
+      <c r="E220" s="261" t="s">
+        <v>362</v>
+      </c>
+      <c r="F220" s="262"/>
+      <c r="G220" s="255"/>
+      <c r="H220" s="255"/>
+      <c r="I220" s="255"/>
+      <c r="J220" s="255"/>
+      <c r="K220" s="255"/>
+      <c r="L220" s="255"/>
+      <c r="M220" s="255"/>
+      <c r="N220" s="255"/>
+    </row>
+    <row r="221" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B221" s="258">
+        <v>3</v>
+      </c>
+      <c r="C221" s="259">
+        <v>46083</v>
+      </c>
+      <c r="D221" s="260">
+        <v>595</v>
+      </c>
+      <c r="E221" s="269" t="s">
+        <v>363</v>
+      </c>
+      <c r="F221" s="262"/>
+      <c r="G221" s="255"/>
+      <c r="H221" s="255"/>
+      <c r="I221" s="255"/>
+      <c r="J221" s="255"/>
+      <c r="K221" s="255"/>
+      <c r="L221" s="255"/>
+      <c r="M221" s="255"/>
+      <c r="N221" s="255"/>
+    </row>
+    <row r="222" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B222" s="258">
+        <v>4</v>
+      </c>
+      <c r="C222" s="259">
+        <v>46083</v>
+      </c>
+      <c r="D222" s="260">
+        <v>600</v>
+      </c>
+      <c r="E222" s="269" t="s">
+        <v>364</v>
+      </c>
+      <c r="F222" s="262"/>
+      <c r="G222" s="255"/>
+      <c r="H222" s="255"/>
+      <c r="I222" s="255"/>
+      <c r="J222" s="255"/>
+      <c r="K222" s="255"/>
+      <c r="L222" s="255"/>
+      <c r="M222" s="255"/>
+      <c r="N222" s="255"/>
+    </row>
+    <row r="223" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B223" s="258">
         <v>5</v>
       </c>
-      <c r="C184" s="260">
-        <v>45909</v>
-      </c>
-      <c r="D184" s="261">
-        <v>340</v>
-      </c>
-      <c r="E184" s="262" t="s">
-        <v>338</v>
-      </c>
-      <c r="F184" s="263"/>
-      <c r="G184" s="256"/>
-      <c r="H184" s="256"/>
-      <c r="I184" s="256"/>
-      <c r="J184" s="256"/>
-      <c r="K184" s="256"/>
-      <c r="L184" s="256"/>
-      <c r="M184" s="256"/>
-      <c r="N184" s="256"/>
-    </row>
-    <row r="185" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B185" s="264" t="s">
+      <c r="C223" s="259">
+        <v>46083</v>
+      </c>
+      <c r="D223" s="260">
+        <v>65</v>
+      </c>
+      <c r="E223" s="269" t="s">
+        <v>365</v>
+      </c>
+      <c r="F223" s="262"/>
+      <c r="G223" s="255"/>
+      <c r="H223" s="255"/>
+      <c r="I223" s="255"/>
+      <c r="J223" s="255"/>
+      <c r="K223" s="255"/>
+      <c r="L223" s="255"/>
+      <c r="M223" s="255"/>
+      <c r="N223" s="255"/>
+    </row>
+    <row r="224" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B224" s="258">
+        <v>6</v>
+      </c>
+      <c r="C224" s="259">
+        <v>46083</v>
+      </c>
+      <c r="D224" s="260">
+        <v>3000</v>
+      </c>
+      <c r="E224" s="269" t="s">
+        <v>366</v>
+      </c>
+      <c r="F224" s="262"/>
+      <c r="G224" s="255"/>
+      <c r="H224" s="255"/>
+      <c r="I224" s="255"/>
+      <c r="J224" s="255"/>
+      <c r="K224" s="255"/>
+      <c r="L224" s="255"/>
+      <c r="M224" s="255"/>
+      <c r="N224" s="255"/>
+    </row>
+    <row r="225" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B225" s="258">
+        <v>7</v>
+      </c>
+      <c r="C225" s="259">
+        <v>46085</v>
+      </c>
+      <c r="D225" s="260">
+        <v>9105</v>
+      </c>
+      <c r="E225" s="269" t="s">
+        <v>367</v>
+      </c>
+      <c r="F225" s="262"/>
+      <c r="G225" s="255"/>
+      <c r="H225" s="255"/>
+      <c r="I225" s="255"/>
+      <c r="J225" s="255"/>
+      <c r="K225" s="255"/>
+      <c r="L225" s="255"/>
+      <c r="M225" s="255"/>
+      <c r="N225" s="255"/>
+    </row>
+    <row r="226" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B226" s="258">
+        <v>8</v>
+      </c>
+      <c r="C226" s="259">
+        <v>46086</v>
+      </c>
+      <c r="D226" s="260">
+        <v>350</v>
+      </c>
+      <c r="E226" s="269" t="s">
+        <v>368</v>
+      </c>
+      <c r="F226" s="262"/>
+      <c r="G226" s="255"/>
+      <c r="H226" s="255"/>
+      <c r="I226" s="255"/>
+      <c r="J226" s="255"/>
+      <c r="K226" s="255"/>
+      <c r="L226" s="255"/>
+      <c r="M226" s="255"/>
+      <c r="N226" s="255"/>
+    </row>
+    <row r="227" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B227" s="258">
+        <v>9</v>
+      </c>
+      <c r="C227" s="259">
+        <v>46086</v>
+      </c>
+      <c r="D227" s="260">
+        <v>10000</v>
+      </c>
+      <c r="E227" s="269" t="s">
+        <v>369</v>
+      </c>
+      <c r="F227" s="271" t="s">
+        <v>370</v>
+      </c>
+      <c r="G227" s="89" t="s">
+        <v>371</v>
+      </c>
+      <c r="H227" s="255"/>
+      <c r="I227" s="255"/>
+      <c r="J227" s="255"/>
+      <c r="K227" s="255"/>
+      <c r="L227" s="255"/>
+      <c r="M227" s="255"/>
+      <c r="N227" s="255"/>
+    </row>
+    <row r="228" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B228" s="258">
+        <v>10</v>
+      </c>
+      <c r="C228" s="259">
+        <v>46089</v>
+      </c>
+      <c r="D228" s="260">
+        <v>300</v>
+      </c>
+      <c r="E228" s="269" t="s">
+        <v>372</v>
+      </c>
+      <c r="F228" s="270"/>
+      <c r="G228" s="262"/>
+      <c r="H228" s="255"/>
+      <c r="I228" s="255"/>
+      <c r="J228" s="255"/>
+      <c r="K228" s="255"/>
+      <c r="L228" s="255"/>
+      <c r="M228" s="255"/>
+      <c r="N228" s="255"/>
+    </row>
+    <row r="229" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B229" s="258">
+        <v>11</v>
+      </c>
+      <c r="C229" s="259">
+        <v>46091</v>
+      </c>
+      <c r="D229" s="260">
+        <v>600</v>
+      </c>
+      <c r="E229" s="269" t="s">
+        <v>373</v>
+      </c>
+      <c r="F229" s="270"/>
+      <c r="G229" s="262"/>
+      <c r="H229" s="255"/>
+      <c r="I229" s="255"/>
+      <c r="J229" s="255"/>
+      <c r="K229" s="255"/>
+      <c r="L229" s="255"/>
+      <c r="M229" s="255"/>
+      <c r="N229" s="255"/>
+    </row>
+    <row r="230" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B230" s="258">
+        <v>12</v>
+      </c>
+      <c r="C230" s="259">
+        <v>46094</v>
+      </c>
+      <c r="D230" s="260">
+        <v>650</v>
+      </c>
+      <c r="E230" s="269" t="s">
+        <v>374</v>
+      </c>
+      <c r="F230" s="270"/>
+      <c r="G230" s="262"/>
+      <c r="H230" s="255"/>
+      <c r="I230" s="255"/>
+      <c r="J230" s="255"/>
+      <c r="K230" s="255"/>
+      <c r="L230" s="255"/>
+      <c r="M230" s="255"/>
+      <c r="N230" s="255"/>
+    </row>
+    <row r="231" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B231" s="258">
+        <v>13</v>
+      </c>
+      <c r="C231" s="259">
+        <v>46094</v>
+      </c>
+      <c r="D231" s="260">
+        <v>2100</v>
+      </c>
+      <c r="E231" s="269" t="s">
+        <v>375</v>
+      </c>
+      <c r="F231" s="89" t="s">
+        <v>376</v>
+      </c>
+      <c r="G231" s="262"/>
+      <c r="H231" s="255"/>
+      <c r="I231" s="255"/>
+      <c r="J231" s="255"/>
+      <c r="K231" s="255"/>
+      <c r="L231" s="255"/>
+      <c r="M231" s="255"/>
+      <c r="N231" s="255"/>
+    </row>
+    <row r="232" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B232" s="258">
+        <v>14</v>
+      </c>
+      <c r="C232" s="259">
+        <v>46101</v>
+      </c>
+      <c r="D232" s="260">
+        <v>2850</v>
+      </c>
+      <c r="E232" s="269" t="s">
+        <v>377</v>
+      </c>
+      <c r="F232" s="270"/>
+      <c r="G232" s="262"/>
+      <c r="H232" s="255"/>
+      <c r="I232" s="255"/>
+      <c r="J232" s="255"/>
+      <c r="K232" s="255"/>
+      <c r="L232" s="255"/>
+      <c r="M232" s="255"/>
+      <c r="N232" s="255"/>
+    </row>
+    <row r="233" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B233" s="258">
+        <v>15</v>
+      </c>
+      <c r="C233" s="259">
+        <v>46101</v>
+      </c>
+      <c r="D233" s="260">
+        <v>900</v>
+      </c>
+      <c r="E233" s="272" t="s">
+        <v>378</v>
+      </c>
+      <c r="F233" s="270"/>
+      <c r="G233" s="262"/>
+      <c r="H233" s="255"/>
+      <c r="I233" s="255"/>
+      <c r="J233" s="255"/>
+      <c r="K233" s="255"/>
+      <c r="L233" s="255"/>
+      <c r="M233" s="255"/>
+      <c r="N233" s="255"/>
+    </row>
+    <row r="234" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B234" s="258"/>
+      <c r="C234" s="260"/>
+      <c r="D234" s="268"/>
+      <c r="E234" s="269"/>
+      <c r="F234" s="274"/>
+      <c r="G234" s="255"/>
+      <c r="H234" s="255"/>
+      <c r="I234" s="255"/>
+      <c r="J234" s="255"/>
+      <c r="K234" s="255"/>
+      <c r="L234" s="255"/>
+      <c r="M234" s="255"/>
+      <c r="N234" s="255"/>
+    </row>
+    <row r="235" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B235" s="263" t="s">
         <v>153</v>
       </c>
-      <c r="C185" s="274"/>
-      <c r="D185" s="265">
-        <v>12994</v>
-      </c>
-      <c r="E185" s="266"/>
-      <c r="F185" s="275"/>
-      <c r="G185" s="256"/>
-      <c r="H185" s="256"/>
-      <c r="I185" s="256"/>
-      <c r="J185" s="256"/>
-      <c r="K185" s="256"/>
-      <c r="L185" s="256"/>
-      <c r="M185" s="256"/>
-      <c r="N185" s="256"/>
-    </row>
-    <row r="186" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B186" s="259">
+      <c r="C235" s="273"/>
+      <c r="D235" s="264">
+        <v>43150</v>
+      </c>
+      <c r="E235" s="265"/>
+      <c r="F235" s="274"/>
+      <c r="G235" s="255"/>
+      <c r="H235" s="255"/>
+      <c r="I235" s="255"/>
+      <c r="J235" s="255"/>
+      <c r="K235" s="255"/>
+      <c r="L235" s="255"/>
+      <c r="M235" s="255"/>
+      <c r="N235" s="255"/>
+    </row>
+    <row r="236" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B236" s="258">
         <v>1</v>
       </c>
-      <c r="C186" s="260">
-        <v>45934</v>
-      </c>
-      <c r="D186" s="261">
-        <v>8787</v>
-      </c>
-      <c r="E186" s="262" t="s">
-        <v>282</v>
-      </c>
-      <c r="F186" s="263"/>
-      <c r="G186" s="256"/>
-      <c r="H186" s="256"/>
-      <c r="I186" s="256"/>
-      <c r="J186" s="256"/>
-      <c r="K186" s="256"/>
-      <c r="L186" s="256"/>
-      <c r="M186" s="256"/>
-      <c r="N186" s="256"/>
-    </row>
-    <row r="187" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B187" s="259">
+      <c r="C236" s="259">
+        <v>46114</v>
+      </c>
+      <c r="D236" s="266">
+        <v>11277</v>
+      </c>
+      <c r="E236" s="261" t="s">
+        <v>379</v>
+      </c>
+      <c r="F236" s="262"/>
+      <c r="G236" s="255"/>
+      <c r="H236" s="255"/>
+      <c r="I236" s="255"/>
+      <c r="J236" s="255"/>
+      <c r="K236" s="255"/>
+      <c r="L236" s="255"/>
+      <c r="M236" s="255"/>
+      <c r="N236" s="255"/>
+    </row>
+    <row r="237" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B237" s="258">
         <v>2</v>
       </c>
-      <c r="C187" s="260">
-        <v>45938</v>
-      </c>
-      <c r="D187" s="261">
+      <c r="C237" s="259">
+        <v>46117</v>
+      </c>
+      <c r="D237" s="266">
+        <v>500</v>
+      </c>
+      <c r="E237" s="261" t="s">
+        <v>380</v>
+      </c>
+      <c r="F237" s="262"/>
+      <c r="G237" s="255"/>
+      <c r="H237" s="255"/>
+      <c r="I237" s="255"/>
+      <c r="J237" s="255"/>
+      <c r="K237" s="255"/>
+      <c r="L237" s="255"/>
+      <c r="M237" s="255"/>
+      <c r="N237" s="255"/>
+    </row>
+    <row r="238" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B238" s="258">
+        <v>3</v>
+      </c>
+      <c r="C238" s="259">
+        <v>46123</v>
+      </c>
+      <c r="D238" s="266">
+        <v>715</v>
+      </c>
+      <c r="E238" s="261" t="s">
+        <v>381</v>
+      </c>
+      <c r="F238" s="262"/>
+      <c r="G238" s="255"/>
+      <c r="H238" s="255"/>
+      <c r="I238" s="255"/>
+      <c r="J238" s="255"/>
+      <c r="K238" s="255"/>
+      <c r="L238" s="255"/>
+      <c r="M238" s="255"/>
+      <c r="N238" s="255"/>
+    </row>
+    <row r="239" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B239" s="263" t="s">
+        <v>153</v>
+      </c>
+      <c r="C239" s="273"/>
+      <c r="D239" s="264">
+        <v>12492</v>
+      </c>
+      <c r="E239" s="265"/>
+      <c r="F239" s="274"/>
+      <c r="G239" s="255"/>
+      <c r="H239" s="255"/>
+      <c r="I239" s="255"/>
+      <c r="J239" s="255"/>
+      <c r="K239" s="255"/>
+      <c r="L239" s="255"/>
+      <c r="M239" s="255"/>
+      <c r="N239" s="255"/>
+    </row>
+    <row r="240" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B240" s="258">
+        <v>1</v>
+      </c>
+      <c r="C240" s="259">
+        <v>46147</v>
+      </c>
+      <c r="D240" s="266">
+        <v>11201</v>
+      </c>
+      <c r="E240" s="261" t="s">
+        <v>382</v>
+      </c>
+      <c r="F240" s="262"/>
+      <c r="G240" s="255"/>
+      <c r="H240" s="255"/>
+      <c r="I240" s="255"/>
+      <c r="J240" s="255"/>
+      <c r="K240" s="255"/>
+      <c r="L240" s="255"/>
+      <c r="M240" s="255"/>
+      <c r="N240" s="255"/>
+    </row>
+    <row r="241" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B241" s="258">
+        <v>2</v>
+      </c>
+      <c r="C241" s="259">
+        <v>46152</v>
+      </c>
+      <c r="D241" s="266">
+        <v>600</v>
+      </c>
+      <c r="E241" s="272" t="s">
+        <v>383</v>
+      </c>
+      <c r="F241" s="262"/>
+      <c r="G241" s="255"/>
+      <c r="H241" s="255"/>
+      <c r="I241" s="255"/>
+      <c r="J241" s="255"/>
+      <c r="K241" s="255"/>
+      <c r="L241" s="255"/>
+      <c r="M241" s="255"/>
+      <c r="N241" s="255"/>
+    </row>
+    <row r="242" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B242" s="263" t="s">
+        <v>153</v>
+      </c>
+      <c r="C242" s="273"/>
+      <c r="D242" s="264">
+        <v>11801</v>
+      </c>
+      <c r="E242" s="265"/>
+    </row>
+    <row r="243" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B243" s="258">
+        <v>1</v>
+      </c>
+      <c r="C243" s="259">
+        <v>46176</v>
+      </c>
+      <c r="D243" s="266">
+        <v>15365</v>
+      </c>
+      <c r="E243" s="261" t="s">
         <v>390</v>
       </c>
-      <c r="E187" s="262" t="s">
-        <v>339</v>
-      </c>
-      <c r="F187" s="263"/>
-      <c r="G187" s="256"/>
-      <c r="H187" s="256"/>
-      <c r="I187" s="256"/>
-      <c r="J187" s="256"/>
-      <c r="K187" s="256"/>
-      <c r="L187" s="256"/>
-      <c r="M187" s="256"/>
-      <c r="N187" s="256"/>
-    </row>
-    <row r="188" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B188" s="259">
-        <v>3</v>
-      </c>
-      <c r="C188" s="260">
-        <v>45941</v>
-      </c>
-      <c r="D188" s="267">
-        <v>500</v>
-      </c>
-      <c r="E188" s="262" t="s">
-        <v>340</v>
-      </c>
-      <c r="F188" s="263"/>
-      <c r="G188" s="256"/>
-      <c r="H188" s="256"/>
-      <c r="I188" s="256"/>
-      <c r="J188" s="256"/>
-      <c r="K188" s="256"/>
-      <c r="L188" s="256"/>
-      <c r="M188" s="256"/>
-      <c r="N188" s="256"/>
-    </row>
-    <row r="189" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B189" s="259">
-        <v>4</v>
-      </c>
-      <c r="C189" s="260">
-        <v>45941</v>
-      </c>
-      <c r="D189" s="267">
-        <v>9500</v>
-      </c>
-      <c r="E189" s="262" t="s">
-        <v>341</v>
-      </c>
-      <c r="F189" s="263"/>
-      <c r="G189" s="256"/>
-      <c r="H189" s="256"/>
-      <c r="I189" s="256"/>
-      <c r="J189" s="256"/>
-      <c r="K189" s="256"/>
-      <c r="L189" s="256"/>
-      <c r="M189" s="256"/>
-      <c r="N189" s="256"/>
-    </row>
-    <row r="190" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B190" s="259">
-        <v>5</v>
-      </c>
-      <c r="C190" s="260">
-        <v>45942</v>
-      </c>
-      <c r="D190" s="267">
-        <v>5000</v>
-      </c>
-      <c r="E190" s="262" t="s">
-        <v>342</v>
-      </c>
-      <c r="F190" s="263"/>
-      <c r="G190" s="256"/>
-      <c r="H190" s="256"/>
-      <c r="I190" s="256"/>
-      <c r="J190" s="256"/>
-      <c r="K190" s="256"/>
-      <c r="L190" s="256"/>
-      <c r="M190" s="256"/>
-      <c r="N190" s="256"/>
-    </row>
-    <row r="191" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B191" s="259">
-        <v>6</v>
-      </c>
-      <c r="C191" s="260">
-        <v>45942</v>
-      </c>
-      <c r="D191" s="267">
-        <v>1500</v>
-      </c>
-      <c r="E191" s="262" t="s">
-        <v>343</v>
-      </c>
-      <c r="F191" s="263"/>
-      <c r="G191" s="256"/>
-      <c r="H191" s="256"/>
-      <c r="I191" s="256"/>
-      <c r="J191" s="256"/>
-      <c r="K191" s="256"/>
-      <c r="L191" s="256"/>
-      <c r="M191" s="256"/>
-      <c r="N191" s="256"/>
-    </row>
-    <row r="192" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B192" s="259">
-        <v>7</v>
-      </c>
-      <c r="C192" s="260">
-        <v>45943</v>
-      </c>
-      <c r="D192" s="267">
-        <v>2000</v>
-      </c>
-      <c r="E192" s="262" t="s">
-        <v>344</v>
-      </c>
-      <c r="F192" s="263"/>
-      <c r="G192" s="256"/>
-      <c r="H192" s="256"/>
-      <c r="I192" s="256"/>
-      <c r="J192" s="256"/>
-      <c r="K192" s="256"/>
-      <c r="L192" s="256"/>
-      <c r="M192" s="256"/>
-      <c r="N192" s="256"/>
-    </row>
-    <row r="193" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B193" s="259">
-        <v>8</v>
-      </c>
-      <c r="C193" s="260">
-        <v>45943</v>
-      </c>
-      <c r="D193" s="267">
-        <v>2500</v>
-      </c>
-      <c r="E193" s="262" t="s">
-        <v>343</v>
-      </c>
-      <c r="F193" s="263"/>
-      <c r="G193" s="256"/>
-      <c r="H193" s="256"/>
-      <c r="I193" s="256"/>
-      <c r="J193" s="256"/>
-      <c r="K193" s="256"/>
-      <c r="L193" s="256"/>
-      <c r="M193" s="256"/>
-      <c r="N193" s="256"/>
-    </row>
-    <row r="194" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B194" s="259">
-        <v>9</v>
-      </c>
-      <c r="C194" s="260">
-        <v>45944</v>
-      </c>
-      <c r="D194" s="267">
-        <v>2000</v>
-      </c>
-      <c r="E194" s="262" t="s">
-        <v>343</v>
-      </c>
-      <c r="F194" s="263"/>
-      <c r="G194" s="256"/>
-      <c r="H194" s="256"/>
-      <c r="I194" s="256"/>
-      <c r="J194" s="256"/>
-      <c r="K194" s="256"/>
-      <c r="L194" s="256"/>
-      <c r="M194" s="256"/>
-      <c r="N194" s="256"/>
-    </row>
-    <row r="195" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B195" s="259">
-        <v>10</v>
-      </c>
-      <c r="C195" s="260">
-        <v>45944</v>
-      </c>
-      <c r="D195" s="267">
-        <v>317</v>
-      </c>
-      <c r="E195" s="262" t="s">
-        <v>345</v>
-      </c>
-      <c r="F195" s="276" t="s">
-        <v>140</v>
-      </c>
-      <c r="G195" s="89"/>
-      <c r="H195" s="256"/>
-      <c r="I195" s="256"/>
-      <c r="J195" s="256"/>
-      <c r="K195" s="256"/>
-      <c r="L195" s="256"/>
-      <c r="M195" s="256"/>
-      <c r="N195" s="256"/>
-    </row>
-    <row r="196" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B196" s="259">
-        <v>11</v>
-      </c>
-      <c r="C196" s="260">
-        <v>45944</v>
-      </c>
-      <c r="D196" s="267">
-        <v>800</v>
-      </c>
-      <c r="E196" s="262" t="s">
-        <v>346</v>
-      </c>
-      <c r="F196" s="263"/>
-      <c r="G196" s="256"/>
-      <c r="H196" s="256"/>
-      <c r="I196" s="256"/>
-      <c r="J196" s="256"/>
-      <c r="K196" s="256"/>
-      <c r="L196" s="256"/>
-      <c r="M196" s="256"/>
-      <c r="N196" s="256"/>
-    </row>
-    <row r="197" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B197" s="259">
-        <v>12</v>
-      </c>
-      <c r="C197" s="260">
-        <v>45945</v>
-      </c>
-      <c r="D197" s="267">
-        <v>800</v>
-      </c>
-      <c r="E197" s="262" t="s">
-        <v>347</v>
-      </c>
-      <c r="F197" s="263"/>
-      <c r="G197" s="256"/>
-      <c r="H197" s="256"/>
-      <c r="I197" s="256"/>
-      <c r="J197" s="256"/>
-      <c r="K197" s="256"/>
-      <c r="L197" s="256"/>
-      <c r="M197" s="256"/>
-      <c r="N197" s="256"/>
-    </row>
-    <row r="198" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B198" s="259">
-        <v>13</v>
-      </c>
-      <c r="C198" s="260">
-        <v>45945</v>
-      </c>
-      <c r="D198" s="267">
-        <v>800</v>
-      </c>
-      <c r="E198" s="262" t="s">
-        <v>348</v>
-      </c>
-      <c r="F198" s="263"/>
-      <c r="G198" s="256"/>
-      <c r="H198" s="256"/>
-      <c r="I198" s="256"/>
-      <c r="J198" s="256"/>
-      <c r="K198" s="256"/>
-      <c r="L198" s="256"/>
-      <c r="M198" s="256"/>
-      <c r="N198" s="256"/>
-    </row>
-    <row r="199" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B199" s="259">
-        <v>14</v>
-      </c>
-      <c r="C199" s="260">
-        <v>45945</v>
-      </c>
-      <c r="D199" s="267">
-        <v>500</v>
-      </c>
-      <c r="E199" s="262" t="s">
-        <v>343</v>
-      </c>
-      <c r="F199" s="263"/>
-      <c r="G199" s="256"/>
-      <c r="H199" s="256"/>
-      <c r="I199" s="256"/>
-      <c r="J199" s="256"/>
-      <c r="K199" s="256"/>
-      <c r="L199" s="256"/>
-      <c r="M199" s="256"/>
-      <c r="N199" s="256"/>
-    </row>
-    <row r="200" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B200" s="259">
-        <v>15</v>
-      </c>
-      <c r="C200" s="260">
-        <v>45946</v>
-      </c>
-      <c r="D200" s="267">
-        <v>1500</v>
-      </c>
-      <c r="E200" s="262" t="s">
-        <v>349</v>
-      </c>
-      <c r="F200" s="263"/>
-      <c r="G200" s="256"/>
-      <c r="H200" s="256"/>
-      <c r="I200" s="256"/>
-      <c r="J200" s="256"/>
-      <c r="K200" s="256"/>
-      <c r="L200" s="256"/>
-      <c r="M200" s="256"/>
-      <c r="N200" s="256"/>
-    </row>
-    <row r="201" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B201" s="259">
-        <v>16</v>
-      </c>
-      <c r="C201" s="260">
-        <v>45947</v>
-      </c>
-      <c r="D201" s="267">
-        <v>15000</v>
-      </c>
-      <c r="E201" s="268" t="s">
-        <v>350</v>
-      </c>
-      <c r="F201" s="276" t="s">
-        <v>140</v>
-      </c>
-      <c r="G201" s="89"/>
-      <c r="H201" s="256"/>
-      <c r="I201" s="256"/>
-      <c r="J201" s="256"/>
-      <c r="K201" s="256"/>
-      <c r="L201" s="256"/>
-      <c r="M201" s="256"/>
-      <c r="N201" s="256"/>
-    </row>
-    <row r="202" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B202" s="259">
-        <v>13</v>
-      </c>
-      <c r="C202" s="260">
-        <v>45948</v>
-      </c>
-      <c r="D202" s="267">
-        <v>5700</v>
-      </c>
-      <c r="E202" s="262" t="s">
-        <v>351</v>
-      </c>
-      <c r="F202" s="263"/>
-      <c r="G202" s="256"/>
-      <c r="H202" s="256"/>
-      <c r="I202" s="256"/>
-      <c r="J202" s="256"/>
-      <c r="K202" s="256"/>
-      <c r="L202" s="256"/>
-      <c r="M202" s="256"/>
-      <c r="N202" s="256"/>
-    </row>
-    <row r="203" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B203" s="259">
-        <v>14</v>
-      </c>
-      <c r="C203" s="260">
-        <v>45953</v>
-      </c>
-      <c r="D203" s="267">
-        <v>500</v>
-      </c>
-      <c r="E203" s="262" t="s">
-        <v>352</v>
-      </c>
-      <c r="F203" s="263"/>
-      <c r="G203" s="256"/>
-      <c r="H203" s="256"/>
-      <c r="I203" s="256"/>
-      <c r="J203" s="256"/>
-      <c r="K203" s="256"/>
-      <c r="L203" s="256"/>
-      <c r="M203" s="256"/>
-      <c r="N203" s="256"/>
-    </row>
-    <row r="204" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B204" s="259">
-        <v>15</v>
-      </c>
-      <c r="C204" s="261"/>
-      <c r="D204" s="269"/>
-      <c r="E204" s="262"/>
-      <c r="F204" s="263"/>
-      <c r="G204" s="256"/>
-      <c r="H204" s="256"/>
-      <c r="I204" s="256"/>
-      <c r="J204" s="256"/>
-      <c r="K204" s="256"/>
-      <c r="L204" s="256"/>
-      <c r="M204" s="256"/>
-      <c r="N204" s="256"/>
-    </row>
-    <row r="205" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B205" s="264" t="s">
+    </row>
+    <row r="244" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B244" s="258">
+        <v>2</v>
+      </c>
+      <c r="C244" s="259">
+        <v>46190</v>
+      </c>
+      <c r="D244" s="266">
+        <v>1090</v>
+      </c>
+      <c r="E244" s="261" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="245" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B245" s="263" t="s">
         <v>153</v>
       </c>
-      <c r="C205" s="274"/>
-      <c r="D205" s="265">
-        <v>58094</v>
-      </c>
-      <c r="E205" s="266"/>
-      <c r="F205" s="275"/>
-      <c r="G205" s="256"/>
-      <c r="H205" s="256"/>
-      <c r="I205" s="256"/>
-      <c r="J205" s="256"/>
-      <c r="K205" s="256"/>
-      <c r="L205" s="256"/>
-      <c r="M205" s="256"/>
-      <c r="N205" s="256"/>
-    </row>
-    <row r="206" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B206" s="259">
-        <v>1</v>
-      </c>
-      <c r="C206" s="260">
-        <v>45966</v>
-      </c>
-      <c r="D206" s="267">
-        <v>11964</v>
-      </c>
-      <c r="E206" s="262" t="s">
-        <v>353</v>
-      </c>
-      <c r="F206" s="263"/>
-      <c r="G206" s="256"/>
-      <c r="H206" s="256"/>
-      <c r="I206" s="256"/>
-      <c r="J206" s="256"/>
-      <c r="K206" s="256"/>
-      <c r="L206" s="256"/>
-      <c r="M206" s="256"/>
-      <c r="N206" s="256"/>
-    </row>
-    <row r="207" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B207" s="259">
-        <v>2</v>
-      </c>
-      <c r="C207" s="260">
-        <v>45967</v>
-      </c>
-      <c r="D207" s="267">
-        <v>500</v>
-      </c>
-      <c r="E207" s="262" t="s">
-        <v>354</v>
-      </c>
-      <c r="F207" s="263"/>
-      <c r="G207" s="256"/>
-      <c r="H207" s="256"/>
-      <c r="I207" s="256"/>
-      <c r="J207" s="256"/>
-      <c r="K207" s="256"/>
-      <c r="L207" s="256"/>
-      <c r="M207" s="256"/>
-      <c r="N207" s="256"/>
-    </row>
-    <row r="208" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B208" s="259">
-        <v>3</v>
-      </c>
-      <c r="C208" s="260">
-        <v>45969</v>
-      </c>
-      <c r="D208" s="261">
-        <v>600</v>
-      </c>
-      <c r="E208" s="262" t="s">
-        <v>355</v>
-      </c>
-      <c r="F208" s="263"/>
-      <c r="G208" s="256"/>
-      <c r="H208" s="256"/>
-      <c r="I208" s="256"/>
-      <c r="J208" s="256"/>
-      <c r="K208" s="256"/>
-      <c r="L208" s="256"/>
-      <c r="M208" s="256"/>
-      <c r="N208" s="256"/>
-    </row>
-    <row r="209" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B209" s="264" t="s">
-        <v>153</v>
-      </c>
-      <c r="C209" s="274"/>
-      <c r="D209" s="265">
-        <v>13064</v>
-      </c>
-      <c r="E209" s="266"/>
-      <c r="F209" s="275"/>
-      <c r="G209" s="256"/>
-      <c r="H209" s="256"/>
-      <c r="I209" s="256"/>
-      <c r="J209" s="256"/>
-      <c r="K209" s="256"/>
-      <c r="L209" s="256"/>
-      <c r="M209" s="256"/>
-      <c r="N209" s="256"/>
-    </row>
-    <row r="210" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B210" s="259">
-        <v>1</v>
-      </c>
-      <c r="C210" s="260">
-        <v>45993</v>
-      </c>
-      <c r="D210" s="267">
-        <v>8784</v>
-      </c>
-      <c r="E210" s="262" t="s">
-        <v>356</v>
-      </c>
-      <c r="F210" s="263"/>
-      <c r="G210" s="256"/>
-      <c r="H210" s="256"/>
-      <c r="I210" s="256"/>
-      <c r="J210" s="256"/>
-      <c r="K210" s="256"/>
-      <c r="L210" s="256"/>
-      <c r="M210" s="256"/>
-      <c r="N210" s="256"/>
-    </row>
-    <row r="211" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B211" s="259">
-        <v>2</v>
-      </c>
-      <c r="C211" s="260">
-        <v>46011</v>
-      </c>
-      <c r="D211" s="267">
-        <v>1570</v>
-      </c>
-      <c r="E211" s="262" t="s">
-        <v>357</v>
-      </c>
-      <c r="F211" s="263"/>
-      <c r="G211" s="256"/>
-      <c r="H211" s="256"/>
-      <c r="I211" s="256"/>
-      <c r="J211" s="256"/>
-      <c r="K211" s="256"/>
-      <c r="L211" s="256"/>
-      <c r="M211" s="256"/>
-      <c r="N211" s="256"/>
-    </row>
-    <row r="212" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B212" s="259">
-        <v>3</v>
-      </c>
-      <c r="C212" s="260">
-        <v>46014</v>
-      </c>
-      <c r="D212" s="261">
-        <v>4000</v>
-      </c>
-      <c r="E212" s="270" t="s">
-        <v>358</v>
-      </c>
-      <c r="F212" s="263"/>
-      <c r="G212" s="256"/>
-      <c r="H212" s="256"/>
-      <c r="I212" s="256"/>
-      <c r="J212" s="256"/>
-      <c r="K212" s="256"/>
-      <c r="L212" s="256"/>
-      <c r="M212" s="256"/>
-      <c r="N212" s="256"/>
-    </row>
-    <row r="213" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B213" s="264" t="s">
-        <v>153</v>
-      </c>
-      <c r="C213" s="274"/>
-      <c r="D213" s="265">
-        <v>14354</v>
-      </c>
-      <c r="E213" s="266"/>
-      <c r="F213" s="275"/>
-      <c r="G213" s="256"/>
-      <c r="H213" s="256"/>
-      <c r="I213" s="256"/>
-      <c r="J213" s="256"/>
-      <c r="K213" s="256"/>
-      <c r="L213" s="256"/>
-      <c r="M213" s="256"/>
-      <c r="N213" s="256"/>
-    </row>
-    <row r="214" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B214" s="259">
-        <v>1</v>
-      </c>
-      <c r="C214" s="260">
-        <v>46023</v>
-      </c>
-      <c r="D214" s="267">
-        <v>9449</v>
-      </c>
-      <c r="E214" s="262" t="s">
-        <v>359</v>
-      </c>
-      <c r="F214" s="263"/>
-      <c r="G214" s="256"/>
-      <c r="H214" s="256"/>
-      <c r="I214" s="256"/>
-      <c r="J214" s="256"/>
-      <c r="K214" s="256"/>
-      <c r="L214" s="256"/>
-      <c r="M214" s="256"/>
-      <c r="N214" s="256"/>
-    </row>
-    <row r="215" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B215" s="264" t="s">
-        <v>153</v>
-      </c>
-      <c r="C215" s="274"/>
-      <c r="D215" s="265">
-        <v>9449</v>
-      </c>
-      <c r="E215" s="266"/>
-      <c r="F215" s="275"/>
-      <c r="G215" s="256"/>
-      <c r="H215" s="256"/>
-      <c r="I215" s="256"/>
-      <c r="J215" s="256"/>
-      <c r="K215" s="256"/>
-      <c r="L215" s="256"/>
-      <c r="M215" s="256"/>
-      <c r="N215" s="256"/>
-    </row>
-    <row r="216" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B216" s="259">
-        <v>1</v>
-      </c>
-      <c r="C216" s="260">
-        <v>46057</v>
-      </c>
-      <c r="D216" s="267">
-        <v>825</v>
-      </c>
-      <c r="E216" s="262" t="s">
-        <v>360</v>
-      </c>
-      <c r="F216" s="263"/>
-      <c r="G216" s="256"/>
-      <c r="H216" s="256"/>
-      <c r="I216" s="256"/>
-      <c r="J216" s="256"/>
-      <c r="K216" s="256"/>
-      <c r="L216" s="256"/>
-      <c r="M216" s="256"/>
-      <c r="N216" s="256"/>
-    </row>
-    <row r="217" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B217" s="259">
-        <v>2</v>
-      </c>
-      <c r="C217" s="260">
-        <v>46057</v>
-      </c>
-      <c r="D217" s="267">
-        <v>9172</v>
-      </c>
-      <c r="E217" s="262" t="s">
-        <v>361</v>
-      </c>
-      <c r="F217" s="263"/>
-      <c r="G217" s="256"/>
-      <c r="H217" s="256"/>
-      <c r="I217" s="256"/>
-      <c r="J217" s="256"/>
-      <c r="K217" s="256"/>
-      <c r="L217" s="256"/>
-      <c r="M217" s="256"/>
-      <c r="N217" s="256"/>
-    </row>
-    <row r="218" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B218" s="264" t="s">
-        <v>153</v>
-      </c>
-      <c r="C218" s="274"/>
-      <c r="D218" s="265">
-        <v>9997</v>
-      </c>
-      <c r="E218" s="266"/>
-      <c r="F218" s="275"/>
-      <c r="G218" s="256"/>
-      <c r="H218" s="256"/>
-      <c r="I218" s="256"/>
-      <c r="J218" s="256"/>
-      <c r="K218" s="256"/>
-      <c r="L218" s="256"/>
-      <c r="M218" s="256"/>
-      <c r="N218" s="256"/>
-    </row>
-    <row r="219" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B219" s="259">
-        <v>1</v>
-      </c>
-      <c r="C219" s="260">
-        <v>46083</v>
-      </c>
-      <c r="D219" s="267">
-        <v>11500</v>
-      </c>
-      <c r="E219" s="262" t="s">
-        <v>362</v>
-      </c>
-      <c r="F219" s="263"/>
-      <c r="G219" s="256"/>
-      <c r="H219" s="256"/>
-      <c r="I219" s="256"/>
-      <c r="J219" s="256"/>
-      <c r="K219" s="256"/>
-      <c r="L219" s="256"/>
-      <c r="M219" s="256"/>
-      <c r="N219" s="256"/>
-    </row>
-    <row r="220" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B220" s="259">
-        <v>2</v>
-      </c>
-      <c r="C220" s="260">
-        <v>46083</v>
-      </c>
-      <c r="D220" s="267">
-        <v>535</v>
-      </c>
-      <c r="E220" s="262" t="s">
-        <v>363</v>
-      </c>
-      <c r="F220" s="263"/>
-      <c r="G220" s="256"/>
-      <c r="H220" s="256"/>
-      <c r="I220" s="256"/>
-      <c r="J220" s="256"/>
-      <c r="K220" s="256"/>
-      <c r="L220" s="256"/>
-      <c r="M220" s="256"/>
-      <c r="N220" s="256"/>
-    </row>
-    <row r="221" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B221" s="259">
-        <v>3</v>
-      </c>
-      <c r="C221" s="260">
-        <v>46083</v>
-      </c>
-      <c r="D221" s="261">
-        <v>595</v>
-      </c>
-      <c r="E221" s="270" t="s">
-        <v>364</v>
-      </c>
-      <c r="F221" s="263"/>
-      <c r="G221" s="256"/>
-      <c r="H221" s="256"/>
-      <c r="I221" s="256"/>
-      <c r="J221" s="256"/>
-      <c r="K221" s="256"/>
-      <c r="L221" s="256"/>
-      <c r="M221" s="256"/>
-      <c r="N221" s="256"/>
-    </row>
-    <row r="222" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B222" s="259">
-        <v>4</v>
-      </c>
-      <c r="C222" s="260">
-        <v>46083</v>
-      </c>
-      <c r="D222" s="261">
-        <v>600</v>
-      </c>
-      <c r="E222" s="270" t="s">
-        <v>365</v>
-      </c>
-      <c r="F222" s="263"/>
-      <c r="G222" s="256"/>
-      <c r="H222" s="256"/>
-      <c r="I222" s="256"/>
-      <c r="J222" s="256"/>
-      <c r="K222" s="256"/>
-      <c r="L222" s="256"/>
-      <c r="M222" s="256"/>
-      <c r="N222" s="256"/>
-    </row>
-    <row r="223" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B223" s="259">
-        <v>5</v>
-      </c>
-      <c r="C223" s="260">
-        <v>46083</v>
-      </c>
-      <c r="D223" s="261">
-        <v>65</v>
-      </c>
-      <c r="E223" s="270" t="s">
-        <v>366</v>
-      </c>
-      <c r="F223" s="263"/>
-      <c r="G223" s="256"/>
-      <c r="H223" s="256"/>
-      <c r="I223" s="256"/>
-      <c r="J223" s="256"/>
-      <c r="K223" s="256"/>
-      <c r="L223" s="256"/>
-      <c r="M223" s="256"/>
-      <c r="N223" s="256"/>
-    </row>
-    <row r="224" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B224" s="259">
-        <v>6</v>
-      </c>
-      <c r="C224" s="260">
-        <v>46083</v>
-      </c>
-      <c r="D224" s="261">
-        <v>3000</v>
-      </c>
-      <c r="E224" s="270" t="s">
-        <v>367</v>
-      </c>
-      <c r="F224" s="263"/>
-      <c r="G224" s="256"/>
-      <c r="H224" s="256"/>
-      <c r="I224" s="256"/>
-      <c r="J224" s="256"/>
-      <c r="K224" s="256"/>
-      <c r="L224" s="256"/>
-      <c r="M224" s="256"/>
-      <c r="N224" s="256"/>
-    </row>
-    <row r="225" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B225" s="259">
-        <v>7</v>
-      </c>
-      <c r="C225" s="260">
-        <v>46085</v>
-      </c>
-      <c r="D225" s="261">
-        <v>9105</v>
-      </c>
-      <c r="E225" s="270" t="s">
-        <v>368</v>
-      </c>
-      <c r="F225" s="263"/>
-      <c r="G225" s="256"/>
-      <c r="H225" s="256"/>
-      <c r="I225" s="256"/>
-      <c r="J225" s="256"/>
-      <c r="K225" s="256"/>
-      <c r="L225" s="256"/>
-      <c r="M225" s="256"/>
-      <c r="N225" s="256"/>
-    </row>
-    <row r="226" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B226" s="259">
-        <v>8</v>
-      </c>
-      <c r="C226" s="260">
-        <v>46086</v>
-      </c>
-      <c r="D226" s="261">
-        <v>350</v>
-      </c>
-      <c r="E226" s="270" t="s">
-        <v>369</v>
-      </c>
-      <c r="F226" s="263"/>
-      <c r="G226" s="256"/>
-      <c r="H226" s="256"/>
-      <c r="I226" s="256"/>
-      <c r="J226" s="256"/>
-      <c r="K226" s="256"/>
-      <c r="L226" s="256"/>
-      <c r="M226" s="256"/>
-      <c r="N226" s="256"/>
-    </row>
-    <row r="227" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B227" s="259">
-        <v>9</v>
-      </c>
-      <c r="C227" s="260">
-        <v>46086</v>
-      </c>
-      <c r="D227" s="261">
-        <v>10000</v>
-      </c>
-      <c r="E227" s="270" t="s">
-        <v>370</v>
-      </c>
-      <c r="F227" s="272" t="s">
-        <v>371</v>
-      </c>
-      <c r="G227" s="89" t="s">
-        <v>372</v>
-      </c>
-      <c r="H227" s="256"/>
-      <c r="I227" s="256"/>
-      <c r="J227" s="256"/>
-      <c r="K227" s="256"/>
-      <c r="L227" s="256"/>
-      <c r="M227" s="256"/>
-      <c r="N227" s="256"/>
-    </row>
-    <row r="228" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B228" s="259">
-        <v>10</v>
-      </c>
-      <c r="C228" s="260">
-        <v>46089</v>
-      </c>
-      <c r="D228" s="261">
-        <v>300</v>
-      </c>
-      <c r="E228" s="270" t="s">
-        <v>373</v>
-      </c>
-      <c r="F228" s="271"/>
-      <c r="G228" s="263"/>
-      <c r="H228" s="256"/>
-      <c r="I228" s="256"/>
-      <c r="J228" s="256"/>
-      <c r="K228" s="256"/>
-      <c r="L228" s="256"/>
-      <c r="M228" s="256"/>
-      <c r="N228" s="256"/>
-    </row>
-    <row r="229" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B229" s="259">
-        <v>11</v>
-      </c>
-      <c r="C229" s="260">
-        <v>46091</v>
-      </c>
-      <c r="D229" s="261">
-        <v>600</v>
-      </c>
-      <c r="E229" s="270" t="s">
-        <v>374</v>
-      </c>
-      <c r="F229" s="271"/>
-      <c r="G229" s="263"/>
-      <c r="H229" s="256"/>
-      <c r="I229" s="256"/>
-      <c r="J229" s="256"/>
-      <c r="K229" s="256"/>
-      <c r="L229" s="256"/>
-      <c r="M229" s="256"/>
-      <c r="N229" s="256"/>
-    </row>
-    <row r="230" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B230" s="259">
-        <v>12</v>
-      </c>
-      <c r="C230" s="260">
-        <v>46094</v>
-      </c>
-      <c r="D230" s="261">
-        <v>650</v>
-      </c>
-      <c r="E230" s="270" t="s">
-        <v>375</v>
-      </c>
-      <c r="F230" s="271"/>
-      <c r="G230" s="263"/>
-      <c r="H230" s="256"/>
-      <c r="I230" s="256"/>
-      <c r="J230" s="256"/>
-      <c r="K230" s="256"/>
-      <c r="L230" s="256"/>
-      <c r="M230" s="256"/>
-      <c r="N230" s="256"/>
-    </row>
-    <row r="231" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B231" s="259">
-        <v>13</v>
-      </c>
-      <c r="C231" s="260">
-        <v>46094</v>
-      </c>
-      <c r="D231" s="261">
-        <v>2100</v>
-      </c>
-      <c r="E231" s="270" t="s">
-        <v>376</v>
-      </c>
-      <c r="F231" s="89" t="s">
-        <v>377</v>
-      </c>
-      <c r="G231" s="263"/>
-      <c r="H231" s="256"/>
-      <c r="I231" s="256"/>
-      <c r="J231" s="256"/>
-      <c r="K231" s="256"/>
-      <c r="L231" s="256"/>
-      <c r="M231" s="256"/>
-      <c r="N231" s="256"/>
-    </row>
-    <row r="232" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B232" s="259">
-        <v>14</v>
-      </c>
-      <c r="C232" s="260">
-        <v>46101</v>
-      </c>
-      <c r="D232" s="261">
-        <v>2850</v>
-      </c>
-      <c r="E232" s="270" t="s">
-        <v>378</v>
-      </c>
-      <c r="F232" s="271"/>
-      <c r="G232" s="263"/>
-      <c r="H232" s="256"/>
-      <c r="I232" s="256"/>
-      <c r="J232" s="256"/>
-      <c r="K232" s="256"/>
-      <c r="L232" s="256"/>
-      <c r="M232" s="256"/>
-      <c r="N232" s="256"/>
-    </row>
-    <row r="233" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B233" s="259">
-        <v>15</v>
-      </c>
-      <c r="C233" s="260">
-        <v>46101</v>
-      </c>
-      <c r="D233" s="261">
-        <v>900</v>
-      </c>
-      <c r="E233" s="273" t="s">
-        <v>379</v>
-      </c>
-      <c r="F233" s="271"/>
-      <c r="G233" s="263"/>
-      <c r="H233" s="256"/>
-      <c r="I233" s="256"/>
-      <c r="J233" s="256"/>
-      <c r="K233" s="256"/>
-      <c r="L233" s="256"/>
-      <c r="M233" s="256"/>
-      <c r="N233" s="256"/>
-    </row>
-    <row r="234" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B234" s="259"/>
-      <c r="C234" s="261"/>
-      <c r="D234" s="269"/>
-      <c r="E234" s="270"/>
-      <c r="F234" s="275"/>
-      <c r="G234" s="256"/>
-      <c r="H234" s="256"/>
-      <c r="I234" s="256"/>
-      <c r="J234" s="256"/>
-      <c r="K234" s="256"/>
-      <c r="L234" s="256"/>
-      <c r="M234" s="256"/>
-      <c r="N234" s="256"/>
-    </row>
-    <row r="235" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B235" s="264" t="s">
-        <v>153</v>
-      </c>
-      <c r="C235" s="274"/>
-      <c r="D235" s="265">
-        <v>43150</v>
-      </c>
-      <c r="E235" s="266"/>
-      <c r="F235" s="275"/>
-      <c r="G235" s="256"/>
-      <c r="H235" s="256"/>
-      <c r="I235" s="256"/>
-      <c r="J235" s="256"/>
-      <c r="K235" s="256"/>
-      <c r="L235" s="256"/>
-      <c r="M235" s="256"/>
-      <c r="N235" s="256"/>
-    </row>
-    <row r="236" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B236" s="259">
-        <v>1</v>
-      </c>
-      <c r="C236" s="260">
-        <v>46114</v>
-      </c>
-      <c r="D236" s="267">
-        <v>11277</v>
-      </c>
-      <c r="E236" s="262" t="s">
-        <v>380</v>
-      </c>
-      <c r="F236" s="263"/>
-      <c r="G236" s="256"/>
-      <c r="H236" s="256"/>
-      <c r="I236" s="256"/>
-      <c r="J236" s="256"/>
-      <c r="K236" s="256"/>
-      <c r="L236" s="256"/>
-      <c r="M236" s="256"/>
-      <c r="N236" s="256"/>
-    </row>
-    <row r="237" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B237" s="259">
-        <v>2</v>
-      </c>
-      <c r="C237" s="260">
-        <v>46117</v>
-      </c>
-      <c r="D237" s="267">
-        <v>500</v>
-      </c>
-      <c r="E237" s="262" t="s">
-        <v>381</v>
-      </c>
-      <c r="F237" s="263"/>
-      <c r="G237" s="256"/>
-      <c r="H237" s="256"/>
-      <c r="I237" s="256"/>
-      <c r="J237" s="256"/>
-      <c r="K237" s="256"/>
-      <c r="L237" s="256"/>
-      <c r="M237" s="256"/>
-      <c r="N237" s="256"/>
-    </row>
-    <row r="238" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B238" s="259">
-        <v>3</v>
-      </c>
-      <c r="C238" s="260">
-        <v>46123</v>
-      </c>
-      <c r="D238" s="267">
-        <v>715</v>
-      </c>
-      <c r="E238" s="262" t="s">
-        <v>382</v>
-      </c>
-      <c r="F238" s="263"/>
-      <c r="G238" s="256"/>
-      <c r="H238" s="256"/>
-      <c r="I238" s="256"/>
-      <c r="J238" s="256"/>
-      <c r="K238" s="256"/>
-      <c r="L238" s="256"/>
-      <c r="M238" s="256"/>
-      <c r="N238" s="256"/>
-    </row>
-    <row r="239" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B239" s="264" t="s">
-        <v>153</v>
-      </c>
-      <c r="C239" s="274"/>
-      <c r="D239" s="265">
-        <v>12492</v>
-      </c>
-      <c r="E239" s="266"/>
-      <c r="F239" s="275"/>
-      <c r="G239" s="256"/>
-      <c r="H239" s="256"/>
-      <c r="I239" s="256"/>
-      <c r="J239" s="256"/>
-      <c r="K239" s="256"/>
-      <c r="L239" s="256"/>
-      <c r="M239" s="256"/>
-      <c r="N239" s="256"/>
-    </row>
-    <row r="240" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B240" s="259">
-        <v>1</v>
-      </c>
-      <c r="C240" s="260">
-        <v>46147</v>
-      </c>
-      <c r="D240" s="267">
-        <v>11201</v>
-      </c>
-      <c r="E240" s="262" t="s">
-        <v>383</v>
-      </c>
-      <c r="F240" s="263"/>
-      <c r="G240" s="256"/>
-      <c r="H240" s="256"/>
-      <c r="I240" s="256"/>
-      <c r="J240" s="256"/>
-      <c r="K240" s="256"/>
-      <c r="L240" s="256"/>
-      <c r="M240" s="256"/>
-      <c r="N240" s="256"/>
-    </row>
-    <row r="241" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B241" s="259">
-        <v>2</v>
-      </c>
-      <c r="C241" s="260">
-        <v>46152</v>
-      </c>
-      <c r="D241" s="267">
-        <v>600</v>
-      </c>
-      <c r="E241" s="273" t="s">
-        <v>384</v>
-      </c>
-      <c r="F241" s="263"/>
-      <c r="G241" s="256"/>
-      <c r="H241" s="256"/>
-      <c r="I241" s="256"/>
-      <c r="J241" s="256"/>
-      <c r="K241" s="256"/>
-      <c r="L241" s="256"/>
-      <c r="M241" s="256"/>
-      <c r="N241" s="256"/>
-    </row>
-    <row r="242" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B242" s="264" t="s">
-        <v>153</v>
-      </c>
-      <c r="C242" s="274"/>
-      <c r="D242" s="265">
-        <v>11801</v>
-      </c>
-      <c r="E242" s="266"/>
-    </row>
-    <row r="243" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B243" s="259">
-        <v>1</v>
-      </c>
-      <c r="C243" s="260">
-        <v>46176</v>
-      </c>
-      <c r="D243" s="267">
-        <v>15365</v>
-      </c>
-      <c r="E243" s="262" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="244" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B244" s="259">
-        <v>2</v>
-      </c>
-      <c r="C244" s="260">
-        <v>46190</v>
-      </c>
-      <c r="D244" s="267">
-        <v>1090</v>
-      </c>
-      <c r="E244" s="262" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="245" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B245" s="264" t="s">
-        <v>153</v>
-      </c>
-      <c r="C245" s="274"/>
-      <c r="D245" s="265">
+      <c r="C245" s="273"/>
+      <c r="D245" s="264">
         <f>SUM(D243:D244)</f>
         <v>16455</v>
       </c>
-      <c r="E245" s="266"/>
+      <c r="E245" s="265"/>
     </row>
     <row r="246" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B246" s="259">
+      <c r="B246" s="258">
         <v>1</v>
       </c>
-      <c r="C246" s="260">
+      <c r="C246" s="259">
         <v>46205</v>
       </c>
-      <c r="D246" s="267">
+      <c r="D246" s="266">
         <v>11746</v>
       </c>
-      <c r="E246" s="262" t="s">
-        <v>396</v>
+      <c r="E246" s="261" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="247" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B247" s="264" t="s">
+      <c r="B247" s="263" t="s">
         <v>153</v>
       </c>
-      <c r="C247" s="274"/>
-      <c r="D247" s="265">
+      <c r="C247" s="273"/>
+      <c r="D247" s="264">
         <f>SUM(D246:D246)</f>
         <v>11746</v>
       </c>
-      <c r="E247" s="266"/>
+      <c r="E247" s="265"/>
+    </row>
+    <row r="248" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B248" s="258">
+        <v>1</v>
+      </c>
+      <c r="C248" s="259">
+        <v>46237</v>
+      </c>
+      <c r="D248" s="266">
+        <v>15569</v>
+      </c>
+      <c r="E248" s="261" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="249" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B249" s="258">
+        <v>2</v>
+      </c>
+      <c r="C249" s="259">
+        <v>46239</v>
+      </c>
+      <c r="D249" s="266">
+        <v>1580</v>
+      </c>
+      <c r="E249" s="261" t="s">
+        <v>399</v>
+      </c>
+      <c r="F249" s="89" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="250" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B250" s="258">
+        <v>3</v>
+      </c>
+      <c r="C250" s="259">
+        <v>46242</v>
+      </c>
+      <c r="D250" s="266">
+        <v>800</v>
+      </c>
+      <c r="E250" s="261" t="s">
+        <v>402</v>
+      </c>
+      <c r="F250" s="89"/>
+    </row>
+    <row r="251" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B251" s="263" t="s">
+        <v>153</v>
+      </c>
+      <c r="C251" s="273"/>
+      <c r="D251" s="264">
+        <f>SUM(D248:D250)</f>
+        <v>17949</v>
+      </c>
+      <c r="E251" s="265"/>
+    </row>
+    <row r="252" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B252" s="258">
+        <v>1</v>
+      </c>
+      <c r="C252" s="259">
+        <v>46267</v>
+      </c>
+      <c r="D252" s="266">
+        <v>14653</v>
+      </c>
+      <c r="E252" s="261" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="253" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B253" s="258">
+        <v>2</v>
+      </c>
+      <c r="C253" s="259"/>
+      <c r="D253" s="266"/>
+      <c r="E253" s="261"/>
+      <c r="F253" s="89"/>
+    </row>
+    <row r="254" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B254" s="258">
+        <v>3</v>
+      </c>
+      <c r="C254" s="259"/>
+      <c r="D254" s="266"/>
+      <c r="E254" s="261"/>
+      <c r="F254" s="89"/>
+    </row>
+    <row r="255" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B255" s="263" t="s">
+        <v>153</v>
+      </c>
+      <c r="C255" s="273"/>
+      <c r="D255" s="264">
+        <f>SUM(D252:D254)</f>
+        <v>14653</v>
+      </c>
+      <c r="E255" s="265"/>
     </row>
   </sheetData>
   <customSheetViews>
@@ -18739,18 +19213,19 @@
     <hyperlink ref="F231" r:id="rId31" display="https://drive.google.com/file/d/16DL251v3MhqogzVBu7BnA1W0zywi31IA/view?usp=sharing" xr:uid="{EC301AA1-5B86-4D6A-A3CB-CFA0DA9FE58F}"/>
     <hyperlink ref="E233" r:id="rId32" location="_msocom_2" display="https://dixit155.github.io/JyotiEnclaveSociety/JES_files/sheet004.htm - _msocom_2" xr:uid="{6D1552C9-06AA-4EDE-BFF5-559BD44EB539}"/>
     <hyperlink ref="E241" r:id="rId33" location="_msocom_3" display="https://dixit155.github.io/JyotiEnclaveSociety/JES_files/sheet004.htm - _msocom_3" xr:uid="{6502EDDC-4325-46E1-B916-B6B71E047A2A}"/>
+    <hyperlink ref="F249" r:id="rId34" xr:uid="{8A050A09-C303-44A3-8DC8-A07444C220FD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId34"/>
-  <drawing r:id="rId35"/>
-  <legacyDrawing r:id="rId36"/>
+  <pageSetup orientation="landscape" r:id="rId35"/>
+  <drawing r:id="rId36"/>
+  <legacyDrawing r:id="rId37"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="B1:G39"/>
+  <dimension ref="B1:G41"/>
   <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.26953125" customWidth="1"/>
@@ -18766,12 +19241,12 @@
       <c r="D1" s="3"/>
     </row>
     <row r="2" spans="2:6" ht="19" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B2" s="352" t="s">
+      <c r="B2" s="355" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="353"/>
-      <c r="D2" s="353"/>
-      <c r="E2" s="353"/>
+      <c r="C2" s="356"/>
+      <c r="D2" s="356"/>
+      <c r="E2" s="356"/>
     </row>
     <row r="3" spans="2:6" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B3" s="52" t="s">
@@ -19114,196 +19589,220 @@
       </c>
     </row>
     <row r="27" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="277">
+      <c r="B27" s="276">
         <v>45839</v>
       </c>
-      <c r="C27" s="278">
+      <c r="C27" s="277">
         <v>46223.57</v>
       </c>
-      <c r="D27" s="278">
+      <c r="D27" s="277">
         <v>69854.77</v>
       </c>
-      <c r="E27" s="279" t="s">
+      <c r="E27" s="278" t="s">
         <v>140</v>
       </c>
-      <c r="F27" s="256"/>
+      <c r="F27" s="255"/>
     </row>
     <row r="28" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="277">
+      <c r="B28" s="276">
         <v>45870</v>
       </c>
-      <c r="C28" s="278">
+      <c r="C28" s="277">
         <v>69854.77</v>
       </c>
-      <c r="D28" s="278">
+      <c r="D28" s="277">
         <v>86236.37</v>
       </c>
-      <c r="E28" s="279" t="s">
+      <c r="E28" s="278" t="s">
         <v>140</v>
       </c>
-      <c r="G28" s="256"/>
+      <c r="G28" s="255"/>
     </row>
     <row r="29" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="277">
+      <c r="B29" s="276">
         <v>45901</v>
       </c>
-      <c r="C29" s="278">
+      <c r="C29" s="277">
         <v>86236.37</v>
       </c>
-      <c r="D29" s="278">
+      <c r="D29" s="277">
         <v>102782.56</v>
       </c>
-      <c r="E29" s="279" t="s">
+      <c r="E29" s="278" t="s">
         <v>140</v>
       </c>
-      <c r="G29" s="256"/>
+      <c r="G29" s="255"/>
     </row>
     <row r="30" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="277">
+      <c r="B30" s="276">
         <v>45931</v>
       </c>
-      <c r="C30" s="278">
+      <c r="C30" s="277">
         <v>102782.56</v>
       </c>
-      <c r="D30" s="278">
+      <c r="D30" s="277">
         <v>72510.759999999995</v>
       </c>
-      <c r="E30" s="279" t="s">
+      <c r="E30" s="278" t="s">
         <v>140</v>
       </c>
-      <c r="G30" s="256"/>
+      <c r="G30" s="255"/>
     </row>
     <row r="31" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="277">
+      <c r="B31" s="276">
         <v>45962</v>
       </c>
-      <c r="C31" s="278">
+      <c r="C31" s="277">
         <v>72510.759999999995</v>
       </c>
-      <c r="D31" s="278">
+      <c r="D31" s="277">
         <v>86458.96</v>
       </c>
-      <c r="E31" s="279" t="s">
+      <c r="E31" s="278" t="s">
         <v>140</v>
       </c>
-      <c r="G31" s="256"/>
+      <c r="G31" s="255"/>
     </row>
     <row r="32" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="277">
+      <c r="B32" s="276">
         <v>45992</v>
       </c>
-      <c r="C32" s="278">
+      <c r="C32" s="277">
         <v>86458.96</v>
       </c>
-      <c r="D32" s="278">
+      <c r="D32" s="277">
         <v>100087.16</v>
       </c>
-      <c r="E32" s="279" t="s">
+      <c r="E32" s="278" t="s">
         <v>140</v>
       </c>
-      <c r="G32" s="256"/>
+      <c r="G32" s="255"/>
     </row>
     <row r="33" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="277">
+      <c r="B33" s="276">
         <v>46023</v>
       </c>
-      <c r="C33" s="278">
+      <c r="C33" s="277">
         <v>100087.16</v>
       </c>
-      <c r="D33" s="278">
+      <c r="D33" s="277">
         <v>119650.36</v>
       </c>
-      <c r="E33" s="279" t="s">
+      <c r="E33" s="278" t="s">
         <v>140</v>
       </c>
-      <c r="G33" s="256"/>
+      <c r="G33" s="255"/>
     </row>
     <row r="34" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="277">
+      <c r="B34" s="276">
         <v>46054</v>
       </c>
-      <c r="C34" s="278">
+      <c r="C34" s="277">
         <v>119650.36</v>
       </c>
-      <c r="D34" s="278">
+      <c r="D34" s="277">
         <v>136045.35999999999</v>
       </c>
-      <c r="E34" s="279" t="s">
+      <c r="E34" s="278" t="s">
         <v>140</v>
       </c>
-      <c r="G34" s="256"/>
+      <c r="G34" s="255"/>
     </row>
     <row r="35" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="277">
+      <c r="B35" s="276">
         <v>46082</v>
       </c>
-      <c r="C35" s="278">
+      <c r="C35" s="277">
         <v>136045.35999999999</v>
       </c>
-      <c r="D35" s="278">
+      <c r="D35" s="277">
         <v>121862.56</v>
       </c>
-      <c r="E35" s="279" t="s">
+      <c r="E35" s="278" t="s">
         <v>140</v>
       </c>
-      <c r="G35" s="256"/>
+      <c r="G35" s="255"/>
     </row>
     <row r="36" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="277">
+      <c r="B36" s="276">
         <v>46113</v>
       </c>
-      <c r="C36" s="278">
+      <c r="C36" s="277">
         <v>121862.56</v>
       </c>
-      <c r="D36" s="278">
+      <c r="D36" s="277">
         <v>138950.56</v>
       </c>
-      <c r="E36" s="279" t="s">
+      <c r="E36" s="278" t="s">
         <v>140</v>
       </c>
-      <c r="G36" s="256"/>
+      <c r="G36" s="255"/>
     </row>
     <row r="37" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="277">
+      <c r="B37" s="276">
         <v>46143</v>
       </c>
-      <c r="C37" s="278">
+      <c r="C37" s="277">
         <v>138950.56</v>
       </c>
-      <c r="D37" s="278">
+      <c r="D37" s="277">
         <v>155749.16</v>
       </c>
-      <c r="E37" s="279" t="s">
+      <c r="E37" s="278" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="277">
+      <c r="B38" s="276">
         <v>46174</v>
       </c>
-      <c r="C38" s="278">
+      <c r="C38" s="277">
         <v>155749.16</v>
       </c>
-      <c r="D38" s="278">
+      <c r="D38" s="277">
         <v>164843.76</v>
       </c>
-      <c r="E38" s="279" t="s">
+      <c r="E38" s="278" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="39" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B39" s="277">
+      <c r="B39" s="276">
         <v>46204</v>
       </c>
-      <c r="C39" s="278">
+      <c r="C39" s="277">
         <v>164843.76</v>
       </c>
-      <c r="D39" s="278">
+      <c r="D39" s="277">
         <v>181655.76</v>
       </c>
-      <c r="E39" s="279" t="s">
+      <c r="E39" s="278" t="s">
         <v>140</v>
       </c>
+    </row>
+    <row r="40" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B40" s="276">
+        <v>46235</v>
+      </c>
+      <c r="C40" s="277">
+        <v>181655.76</v>
+      </c>
+      <c r="D40" s="277">
+        <v>195144.16</v>
+      </c>
+      <c r="E40" s="278" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B41" s="276">
+        <v>46266</v>
+      </c>
+      <c r="C41" s="277">
+        <v>195144.16</v>
+      </c>
+      <c r="D41" s="277"/>
+      <c r="E41" s="278"/>
     </row>
   </sheetData>
   <customSheetViews>
@@ -19354,17 +19853,18 @@
     <hyperlink ref="E37" r:id="rId35" display="https://drive.google.com/file/d/1-bMLSFM8Q8Ci3ayrXeC9LX7p_pFxXtco/view?usp=sharing" xr:uid="{662680A5-A1E1-43DC-9697-94812CE480DA}"/>
     <hyperlink ref="E38" r:id="rId36" xr:uid="{B2F0F96A-D133-4F24-AB05-BFA7C9E7C2C2}"/>
     <hyperlink ref="E39" r:id="rId37" xr:uid="{DA52E99A-BB38-4C40-85A0-31687F9FC963}"/>
+    <hyperlink ref="E40" r:id="rId38" xr:uid="{18D5200C-05B8-424F-9234-AC498499BD03}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId38"/>
-  <drawing r:id="rId39"/>
+  <pageSetup orientation="landscape" r:id="rId39"/>
+  <drawing r:id="rId40"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="B1:H45"/>
+  <dimension ref="B1:H47"/>
   <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.26953125" customWidth="1"/>
@@ -19378,12 +19878,12 @@
       <c r="B1" s="9"/>
     </row>
     <row r="2" spans="2:5" ht="19" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="354" t="s">
+      <c r="B2" s="357" t="s">
         <v>192</v>
       </c>
-      <c r="C2" s="355"/>
-      <c r="D2" s="355"/>
-      <c r="E2" s="355"/>
+      <c r="C2" s="358"/>
+      <c r="D2" s="358"/>
+      <c r="E2" s="358"/>
     </row>
     <row r="3" spans="2:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B3" s="69" t="s">
@@ -19792,202 +20292,230 @@
       </c>
     </row>
     <row r="32" spans="2:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="280">
+      <c r="B32" s="279">
         <v>45809</v>
       </c>
-      <c r="C32" s="281">
+      <c r="C32" s="280">
         <v>10057</v>
       </c>
-      <c r="D32" s="282" t="s">
+      <c r="D32" s="281" t="s">
         <v>195</v>
       </c>
-      <c r="E32" s="283" t="s">
+      <c r="E32" s="282" t="s">
         <v>140</v>
       </c>
-      <c r="F32" s="263"/>
-      <c r="G32" s="256"/>
+      <c r="F32" s="262"/>
+      <c r="G32" s="255"/>
     </row>
     <row r="33" spans="2:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="280">
+      <c r="B33" s="279">
         <v>45839</v>
       </c>
-      <c r="C33" s="281">
+      <c r="C33" s="280">
         <v>8660</v>
       </c>
-      <c r="D33" s="282" t="s">
+      <c r="D33" s="281" t="s">
         <v>195</v>
       </c>
-      <c r="E33" s="283" t="s">
+      <c r="E33" s="282" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="34" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="284">
+      <c r="B34" s="283">
         <v>45870</v>
       </c>
-      <c r="C34" s="285">
+      <c r="C34" s="284">
         <v>10273</v>
       </c>
-      <c r="D34" s="286" t="s">
+      <c r="D34" s="285" t="s">
         <v>195</v>
       </c>
-      <c r="E34" s="283" t="s">
+      <c r="E34" s="282" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="287">
+      <c r="B35" s="286">
         <v>45901</v>
       </c>
-      <c r="C35" s="288">
+      <c r="C35" s="287">
         <v>9934</v>
       </c>
-      <c r="D35" s="289" t="s">
+      <c r="D35" s="288" t="s">
         <v>195</v>
       </c>
-      <c r="E35" s="290" t="s">
+      <c r="E35" s="289" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="287">
+      <c r="B36" s="286">
         <v>45931</v>
       </c>
-      <c r="C36" s="288">
+      <c r="C36" s="287">
         <v>8787</v>
       </c>
-      <c r="D36" s="289" t="s">
+      <c r="D36" s="288" t="s">
         <v>195</v>
       </c>
-      <c r="E36" s="290" t="s">
+      <c r="E36" s="289" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="287">
+      <c r="B37" s="286">
         <v>45962</v>
       </c>
-      <c r="C37" s="288">
+      <c r="C37" s="287">
         <v>11964</v>
       </c>
-      <c r="D37" s="289" t="s">
+      <c r="D37" s="288" t="s">
         <v>195</v>
       </c>
-      <c r="E37" s="290" t="s">
+      <c r="E37" s="289" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="38" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="287">
+      <c r="B38" s="286">
         <v>46357</v>
       </c>
-      <c r="C38" s="288">
+      <c r="C38" s="287">
         <v>8784</v>
       </c>
-      <c r="D38" s="289" t="s">
+      <c r="D38" s="288" t="s">
         <v>195</v>
       </c>
-      <c r="E38" s="290" t="s">
+      <c r="E38" s="289" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="39" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B39" s="287">
+      <c r="B39" s="286">
         <v>46023</v>
       </c>
-      <c r="C39" s="288">
+      <c r="C39" s="287">
         <v>9449</v>
       </c>
-      <c r="D39" s="289" t="s">
+      <c r="D39" s="288" t="s">
         <v>195</v>
       </c>
-      <c r="E39" s="290" t="s">
+      <c r="E39" s="289" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="287">
+      <c r="B40" s="286">
         <v>46054</v>
       </c>
-      <c r="C40" s="288">
+      <c r="C40" s="287">
         <v>9172</v>
       </c>
-      <c r="D40" s="289" t="s">
+      <c r="D40" s="288" t="s">
         <v>195</v>
       </c>
-      <c r="E40" s="290" t="s">
+      <c r="E40" s="289" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="287">
+      <c r="B41" s="286">
         <v>46082</v>
       </c>
-      <c r="C41" s="288">
+      <c r="C41" s="287">
         <v>9105</v>
       </c>
-      <c r="D41" s="289" t="s">
+      <c r="D41" s="288" t="s">
         <v>195</v>
       </c>
-      <c r="E41" s="290" t="s">
+      <c r="E41" s="289" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="287">
+      <c r="B42" s="286">
         <v>46113</v>
       </c>
-      <c r="C42" s="288">
+      <c r="C42" s="287">
         <v>11277</v>
       </c>
-      <c r="D42" s="289" t="s">
+      <c r="D42" s="288" t="s">
         <v>195</v>
       </c>
-      <c r="E42" s="290" t="s">
+      <c r="E42" s="289" t="s">
         <v>140</v>
       </c>
-      <c r="G42" s="256"/>
-      <c r="H42" s="263"/>
+      <c r="G42" s="255"/>
+      <c r="H42" s="262"/>
     </row>
     <row r="43" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B43" s="287">
+      <c r="B43" s="286">
         <v>46143</v>
       </c>
-      <c r="C43" s="288">
+      <c r="C43" s="287">
         <v>11201</v>
       </c>
-      <c r="D43" s="289" t="s">
+      <c r="D43" s="288" t="s">
         <v>195</v>
       </c>
-      <c r="E43" s="290" t="s">
+      <c r="E43" s="289" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="287">
+      <c r="B44" s="286">
         <v>46174</v>
       </c>
-      <c r="C44" s="288">
+      <c r="C44" s="287">
         <v>15365</v>
       </c>
-      <c r="D44" s="289" t="s">
+      <c r="D44" s="288" t="s">
         <v>195</v>
       </c>
-      <c r="E44" s="290" t="s">
+      <c r="E44" s="289" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B45" s="287">
+      <c r="B45" s="286">
         <v>46204</v>
       </c>
-      <c r="C45" s="288">
+      <c r="C45" s="287">
         <v>11746</v>
       </c>
-      <c r="D45" s="289" t="s">
+      <c r="D45" s="288" t="s">
         <v>195</v>
       </c>
-      <c r="E45" s="290" t="s">
+      <c r="E45" s="289" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B46" s="286">
+        <v>46235</v>
+      </c>
+      <c r="C46" s="287">
+        <v>15569</v>
+      </c>
+      <c r="D46" s="288" t="s">
+        <v>195</v>
+      </c>
+      <c r="E46" s="289" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B47" s="286">
+        <v>46266</v>
+      </c>
+      <c r="C47" s="287">
+        <v>14653</v>
+      </c>
+      <c r="D47" s="288" t="s">
+        <v>195</v>
+      </c>
+      <c r="E47" s="289" t="s">
         <v>140</v>
       </c>
     </row>
@@ -20047,10 +20575,12 @@
     <hyperlink ref="E43" r:id="rId41" display="https://drive.google.com/file/d/1KH2TjYSKZDmo64nUNtF-nv2fQVhnmmLn/view?usp=sharing" xr:uid="{F3139DB5-CA02-480C-AAD1-817E0C2E97EF}"/>
     <hyperlink ref="E44" r:id="rId42" xr:uid="{B5245485-97C8-4831-9DE6-CD4D3EC10572}"/>
     <hyperlink ref="E45" r:id="rId43" xr:uid="{8EB6956A-CF5D-4194-A1BC-680C69000D27}"/>
+    <hyperlink ref="E47" r:id="rId44" xr:uid="{7B90FEF3-3BFF-448B-AFCA-AF6D807F355E}"/>
+    <hyperlink ref="E46" r:id="rId45" xr:uid="{AE7FB457-1C90-4996-B53E-C683A2531244}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="portrait" r:id="rId44"/>
-  <drawing r:id="rId45"/>
+  <pageSetup orientation="portrait" r:id="rId46"/>
+  <drawing r:id="rId47"/>
 </worksheet>
 </file>
 
@@ -20071,11 +20601,11 @@
       <c r="B1" s="9"/>
     </row>
     <row r="2" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="356" t="s">
+      <c r="B2" s="359" t="s">
         <v>196</v>
       </c>
-      <c r="C2" s="357"/>
-      <c r="D2" s="358"/>
+      <c r="C2" s="360"/>
+      <c r="D2" s="361"/>
     </row>
     <row r="3" spans="2:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B3" s="73" t="s">
@@ -20184,7 +20714,7 @@
         <v>45613</v>
       </c>
       <c r="D12" s="88" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="14.5" x14ac:dyDescent="0.35">
@@ -20195,7 +20725,7 @@
         <v>45628</v>
       </c>
       <c r="D13" s="88" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G13" s="6"/>
     </row>
@@ -20207,7 +20737,7 @@
         <v>45657</v>
       </c>
       <c r="D14" s="88" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="15" spans="2:7" ht="14.5" x14ac:dyDescent="0.35">
@@ -20218,7 +20748,7 @@
         <v>45761</v>
       </c>
       <c r="D15" s="88" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="14.5" x14ac:dyDescent="0.35">
@@ -20229,7 +20759,7 @@
         <v>45765</v>
       </c>
       <c r="D16" s="88" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="14.5" x14ac:dyDescent="0.35">
@@ -20240,7 +20770,7 @@
         <v>45805</v>
       </c>
       <c r="D17" s="88" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -20315,13 +20845,13 @@
       <c r="F1" s="33"/>
     </row>
     <row r="2" spans="2:16" ht="19" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B2" s="341" t="s">
+      <c r="B2" s="344" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="342"/>
-      <c r="D2" s="342"/>
-      <c r="E2" s="342"/>
-      <c r="F2" s="342"/>
+      <c r="C2" s="345"/>
+      <c r="D2" s="345"/>
+      <c r="E2" s="345"/>
+      <c r="F2" s="345"/>
       <c r="G2" s="31">
         <f t="shared" ref="G2:P2" si="0">SUM(G4:G60)</f>
         <v>500</v>
@@ -21659,7 +22189,7 @@
         <v>102</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E44" s="14"/>
       <c r="F44" s="18" t="s">
@@ -22051,7 +22581,7 @@
         <v>129</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E57" s="14"/>
       <c r="F57" s="18" t="s">
@@ -22227,25 +22757,25 @@
       <c r="B1" s="78"/>
     </row>
     <row r="2" spans="2:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B2" s="359" t="s">
-        <v>320</v>
-      </c>
-      <c r="C2" s="360"/>
-      <c r="D2" s="360"/>
+      <c r="B2" s="362" t="s">
+        <v>319</v>
+      </c>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
       <c r="E2" s="200"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B3" s="201" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C3" s="199" t="s">
+        <v>317</v>
+      </c>
+      <c r="D3" s="199" t="s">
         <v>318</v>
       </c>
-      <c r="D3" s="199" t="s">
-        <v>319</v>
-      </c>
       <c r="E3" s="202" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.35">
@@ -22259,7 +22789,7 @@
         <v>600</v>
       </c>
       <c r="E4" s="195" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.35">
@@ -22273,90 +22803,90 @@
         <v>600</v>
       </c>
       <c r="E5" s="206" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B6" s="291">
+      <c r="B6" s="290">
         <v>107</v>
       </c>
-      <c r="C6" s="292">
+      <c r="C6" s="291">
         <v>45894</v>
       </c>
-      <c r="D6" s="293">
-        <v>600</v>
-      </c>
-      <c r="E6" s="262" t="s">
+      <c r="D6" s="292">
+        <v>600</v>
+      </c>
+      <c r="E6" s="261" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="293">
+        <v>108</v>
+      </c>
+      <c r="C7" s="294">
+        <v>45968</v>
+      </c>
+      <c r="D7" s="295">
+        <v>600</v>
+      </c>
+      <c r="E7" s="296" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="294">
-        <v>108</v>
-      </c>
-      <c r="C7" s="295">
-        <v>45968</v>
-      </c>
-      <c r="D7" s="296">
-        <v>600</v>
-      </c>
-      <c r="E7" s="297" t="s">
+    <row r="8" spans="2:5" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B8" s="364" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="8" spans="2:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B8" s="361" t="s">
+      <c r="C8" s="365"/>
+      <c r="D8" s="366"/>
+      <c r="E8" s="297"/>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B9" s="298" t="s">
+        <v>321</v>
+      </c>
+      <c r="C9" s="299" t="s">
+        <v>317</v>
+      </c>
+      <c r="D9" s="299" t="s">
+        <v>318</v>
+      </c>
+      <c r="E9" s="300" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B10" s="290">
+        <v>107</v>
+      </c>
+      <c r="C10" s="291">
+        <v>46073</v>
+      </c>
+      <c r="D10" s="292">
+        <v>600</v>
+      </c>
+      <c r="E10" s="261" t="s">
         <v>387</v>
       </c>
-      <c r="C8" s="362"/>
-      <c r="D8" s="363"/>
-      <c r="E8" s="298"/>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B9" s="299" t="s">
-        <v>322</v>
-      </c>
-      <c r="C9" s="300" t="s">
-        <v>318</v>
-      </c>
-      <c r="D9" s="300" t="s">
-        <v>319</v>
-      </c>
-      <c r="E9" s="301" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B10" s="291">
-        <v>107</v>
-      </c>
-      <c r="C10" s="292">
-        <v>46073</v>
-      </c>
-      <c r="D10" s="293">
-        <v>600</v>
-      </c>
-      <c r="E10" s="262" t="s">
-        <v>388</v>
-      </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B11" s="291"/>
-      <c r="C11" s="302"/>
-      <c r="D11" s="293"/>
-      <c r="E11" s="262"/>
+      <c r="B11" s="290"/>
+      <c r="C11" s="301"/>
+      <c r="D11" s="292"/>
+      <c r="E11" s="261"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B12" s="291"/>
-      <c r="C12" s="302"/>
-      <c r="D12" s="293"/>
-      <c r="E12" s="262"/>
+      <c r="B12" s="290"/>
+      <c r="C12" s="301"/>
+      <c r="D12" s="292"/>
+      <c r="E12" s="261"/>
     </row>
     <row r="13" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="294"/>
-      <c r="C13" s="303"/>
-      <c r="D13" s="296"/>
-      <c r="E13" s="297"/>
+      <c r="B13" s="293"/>
+      <c r="C13" s="302"/>
+      <c r="D13" s="295"/>
+      <c r="E13" s="296"/>
     </row>
   </sheetData>
   <mergeCells count="2">
